--- a/refundable_samples_rollup.xlsx
+++ b/refundable_samples_rollup.xlsx
@@ -799,7 +799,7 @@
         <v>166</v>
       </c>
       <c r="L4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M4">
         <v>16</v>
@@ -5131,7 +5131,7 @@
         <v>3</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70">
         <v>2</v>
@@ -7749,7 +7749,7 @@
         <v>12</v>
       </c>
       <c r="L110">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M110">
         <v>3</v>

--- a/refundable_samples_rollup.xlsx
+++ b/refundable_samples_rollup.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="62">
   <si>
     <t>view</t>
   </si>
@@ -557,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V152"/>
+  <dimension ref="A1:V153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1000,10 +1000,10 @@
         <v>314.7</v>
       </c>
       <c r="K7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M7">
         <v>53</v>
@@ -1077,7 +1077,7 @@
         <v>49</v>
       </c>
       <c r="N8">
-        <v>5626.93</v>
+        <v>5627.16</v>
       </c>
       <c r="O8">
         <v>1224.98</v>
@@ -1340,13 +1340,13 @@
         <v>54.11</v>
       </c>
       <c r="K12">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L12">
         <v>11</v>
       </c>
       <c r="M12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N12">
         <v>470.92</v>
@@ -1364,7 +1364,7 @@
         <v>3.1</v>
       </c>
       <c r="S12">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="T12">
         <v>8.699999999999999</v>
@@ -2342,10 +2342,10 @@
         <v>274.75</v>
       </c>
       <c r="K27">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L27">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M27">
         <v>49</v>
@@ -2419,7 +2419,7 @@
         <v>47</v>
       </c>
       <c r="N28">
-        <v>5607.94</v>
+        <v>5608.17</v>
       </c>
       <c r="O28">
         <v>1205.99</v>
@@ -4026,13 +4026,13 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53">
         <v>0</v>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="S53">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V53">
         <v>64.01000000000001</v>
@@ -5562,16 +5562,16 @@
         <v>40</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F77">
-        <v>24.99</v>
+        <v>142.74</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -5586,13 +5586,13 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L77">
         <v>1</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N77">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="S77">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="V77">
-        <v>24.99</v>
+        <v>142.74</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -5624,16 +5624,16 @@
         <v>40</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F78">
-        <v>91.26000000000001</v>
+        <v>176.62</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -5648,13 +5648,13 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L78">
         <v>1</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N78">
         <v>200.83</v>
@@ -5672,10 +5672,10 @@
         <v>0</v>
       </c>
       <c r="S78">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="V78">
-        <v>91.26000000000001</v>
+        <v>176.62</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -5686,58 +5686,64 @@
         <v>40</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F79">
-        <v>29.39</v>
+        <v>565.6799999999999</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>39.99</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>23.91</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="K79">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>202.33</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>202.33</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q79" t="s">
         <v>52</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S79">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="T79">
+        <v>35.6</v>
+      </c>
+      <c r="U79">
+        <v>35.6</v>
       </c>
       <c r="V79">
-        <v>29.39</v>
+        <v>541.77</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -5748,58 +5754,64 @@
         <v>40</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="D80">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="E80">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="F80">
-        <v>177.93</v>
+        <v>3096.64</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>239.96</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>132.06</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>29.53</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L80">
         <v>0</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>239.22</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>239.22</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q80" t="s">
         <v>53</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>12.6</v>
+      </c>
+      <c r="T80">
+        <v>8.1</v>
+      </c>
+      <c r="U80">
+        <v>8.1</v>
       </c>
       <c r="V80">
-        <v>177.93</v>
+        <v>2964.58</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -5810,64 +5822,64 @@
         <v>40</v>
       </c>
       <c r="C81">
-        <v>24</v>
+        <v>229</v>
       </c>
       <c r="D81">
-        <v>23</v>
+        <v>225</v>
       </c>
       <c r="E81">
-        <v>24</v>
+        <v>229</v>
       </c>
       <c r="F81">
-        <v>803.4</v>
+        <v>6463.77</v>
       </c>
       <c r="G81">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H81">
-        <v>439.95</v>
+        <v>999.87</v>
       </c>
       <c r="I81">
-        <v>197.65</v>
+        <v>412.54</v>
       </c>
       <c r="J81">
-        <v>53.78</v>
+        <v>120.13</v>
       </c>
       <c r="K81">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="L81">
         <v>21</v>
       </c>
       <c r="M81">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="N81">
-        <v>1139.83</v>
+        <v>1371.68</v>
       </c>
       <c r="O81">
-        <v>342.53</v>
+        <v>574.38</v>
       </c>
       <c r="P81">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q81" t="s">
         <v>54</v>
       </c>
       <c r="R81">
-        <v>20.8</v>
+        <v>5.7</v>
       </c>
       <c r="S81">
-        <v>34.8</v>
+        <v>11.6</v>
       </c>
       <c r="T81">
-        <v>21.2</v>
+        <v>11.4</v>
       </c>
       <c r="U81">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="V81">
-        <v>605.75</v>
+        <v>6051.23</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -5878,64 +5890,64 @@
         <v>40</v>
       </c>
       <c r="C82">
-        <v>23</v>
+        <v>345</v>
       </c>
       <c r="D82">
-        <v>23</v>
+        <v>342</v>
       </c>
       <c r="E82">
-        <v>23</v>
+        <v>345</v>
       </c>
       <c r="F82">
-        <v>639.17</v>
+        <v>9824.559999999999</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H82">
-        <v>99.97</v>
+        <v>1259.8</v>
       </c>
       <c r="I82">
-        <v>59.89</v>
+        <v>555.6799999999999</v>
       </c>
       <c r="J82">
-        <v>18.06</v>
+        <v>156.44</v>
       </c>
       <c r="K82">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="L82">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M82">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="N82">
-        <v>207.58</v>
+        <v>432.43</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>224.85</v>
       </c>
       <c r="P82">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q82" t="s">
         <v>55</v>
       </c>
       <c r="R82">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="S82">
-        <v>34.8</v>
+        <v>10.2</v>
       </c>
       <c r="T82">
-        <v>11.5</v>
+        <v>2.8</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V82">
-        <v>579.28</v>
+        <v>9268.879999999999</v>
       </c>
     </row>
     <row r="83" spans="1:22">
@@ -5946,64 +5958,64 @@
         <v>40</v>
       </c>
       <c r="C83">
-        <v>22</v>
+        <v>277</v>
       </c>
       <c r="D83">
-        <v>22</v>
+        <v>274</v>
       </c>
       <c r="E83">
-        <v>22</v>
+        <v>277</v>
       </c>
       <c r="F83">
-        <v>812.03</v>
+        <v>8709.120000000001</v>
       </c>
       <c r="G83">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H83">
-        <v>239.97</v>
+        <v>1419.8</v>
       </c>
       <c r="I83">
-        <v>108.2</v>
+        <v>623.85</v>
       </c>
       <c r="J83">
-        <v>27.46</v>
+        <v>173.21</v>
       </c>
       <c r="K83">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="L83">
         <v>28</v>
       </c>
       <c r="M83">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="N83">
-        <v>24.44</v>
+        <v>122.95</v>
       </c>
       <c r="O83">
-        <v>24.44</v>
+        <v>122.95</v>
       </c>
       <c r="P83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q83" t="s">
         <v>56</v>
       </c>
       <c r="R83">
-        <v>13.6</v>
+        <v>7.2</v>
       </c>
       <c r="S83">
-        <v>45.5</v>
+        <v>10.2</v>
       </c>
       <c r="T83">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="U83">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="V83">
-        <v>703.83</v>
+        <v>8085.27</v>
       </c>
     </row>
     <row r="84" spans="1:22">
@@ -6017,13 +6029,13 @@
         <v>9</v>
       </c>
       <c r="D84">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E84">
         <v>9</v>
       </c>
       <c r="F84">
-        <v>201.05</v>
+        <v>215.31</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -6056,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="Q84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R84">
         <v>0</v>
@@ -6065,7 +6077,7 @@
         <v>0</v>
       </c>
       <c r="V84">
-        <v>201.05</v>
+        <v>215.31</v>
       </c>
     </row>
     <row r="85" spans="1:22">
@@ -6076,58 +6088,64 @@
         <v>40</v>
       </c>
       <c r="C85">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="D85">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="E85">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="F85">
-        <v>692.2</v>
+        <v>2360.48</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>604.9</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>278.51</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>56.27</v>
       </c>
       <c r="K85">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L85">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M85">
         <v>3</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>14.24</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>14.24</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S85">
-        <v>11.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="T85">
+        <v>0.3</v>
+      </c>
+      <c r="U85">
+        <v>0.3</v>
       </c>
       <c r="V85">
-        <v>692.2</v>
+        <v>2081.97</v>
       </c>
     </row>
     <row r="86" spans="1:22">
@@ -6138,58 +6156,64 @@
         <v>40</v>
       </c>
       <c r="C86">
-        <v>15</v>
+        <v>328</v>
       </c>
       <c r="D86">
-        <v>15</v>
+        <v>311</v>
       </c>
       <c r="E86">
-        <v>15</v>
+        <v>328</v>
       </c>
       <c r="F86">
-        <v>458.82</v>
+        <v>6557.21</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>539.98</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>215.94</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>63.25</v>
       </c>
       <c r="K86">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="L86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M86">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N86">
-        <v>127.11</v>
+        <v>80.09</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>80.09</v>
       </c>
       <c r="P86">
         <v>3</v>
       </c>
       <c r="Q86" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S86">
-        <v>26.7</v>
+        <v>3.9</v>
+      </c>
+      <c r="T86">
+        <v>1.3</v>
+      </c>
+      <c r="U86">
+        <v>1.3</v>
       </c>
       <c r="V86">
-        <v>458.82</v>
+        <v>6341.27</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -6200,58 +6224,64 @@
         <v>40</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>224</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>222</v>
       </c>
       <c r="E87">
-        <v>10</v>
+        <v>224</v>
       </c>
       <c r="F87">
-        <v>288.67</v>
+        <v>5486.67</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>229.98</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>113.34</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>37.04</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>151.8</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>24.69</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q87" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>3.2</v>
+      </c>
+      <c r="T87">
+        <v>4.1</v>
+      </c>
+      <c r="U87">
+        <v>0.7</v>
       </c>
       <c r="V87">
-        <v>288.67</v>
+        <v>5373.33</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -6259,40 +6289,40 @@
         <v>24</v>
       </c>
       <c r="B88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="E88">
-        <v>1</v>
+        <v>175</v>
       </c>
       <c r="F88">
-        <v>23.49</v>
+        <v>4224.82</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
       <c r="H88">
-        <v>39.99</v>
+        <v>20</v>
       </c>
       <c r="I88">
-        <v>23.49</v>
+        <v>7.43</v>
       </c>
       <c r="J88">
-        <v>5.69</v>
+        <v>4.73</v>
       </c>
       <c r="K88">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
       <c r="M88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N88">
         <v>0</v>
@@ -6304,13 +6334,13 @@
         <v>0</v>
       </c>
       <c r="Q88" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="R88">
-        <v>100</v>
+        <v>0.6</v>
       </c>
       <c r="S88">
-        <v>100</v>
+        <v>1.9</v>
       </c>
       <c r="T88">
         <v>0</v>
@@ -6319,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>4217.39</v>
       </c>
     </row>
     <row r="89" spans="1:22">
@@ -6330,64 +6360,64 @@
         <v>41</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89">
-        <v>82.98</v>
+        <v>23.49</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89">
-        <v>119.99</v>
+        <v>39.99</v>
       </c>
       <c r="I89">
-        <v>57.99</v>
+        <v>23.49</v>
       </c>
       <c r="J89">
-        <v>12.46</v>
+        <v>5.69</v>
       </c>
       <c r="K89">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L89">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N89">
-        <v>39.89</v>
+        <v>0</v>
       </c>
       <c r="O89">
         <v>0</v>
       </c>
       <c r="P89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R89">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S89">
         <v>100</v>
       </c>
       <c r="T89">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U89">
         <v>0</v>
       </c>
       <c r="V89">
-        <v>24.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:22">
@@ -6398,16 +6428,16 @@
         <v>41</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90">
-        <v>72.39</v>
+        <v>27.99</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -6422,13 +6452,13 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90">
         <v>0</v>
@@ -6440,16 +6470,16 @@
         <v>0</v>
       </c>
       <c r="Q90" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R90">
         <v>0</v>
       </c>
       <c r="S90">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V90">
-        <v>72.39</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="91" spans="1:22">
@@ -6460,40 +6490,40 @@
         <v>41</v>
       </c>
       <c r="C91">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E91">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F91">
-        <v>179.6</v>
+        <v>122.97</v>
       </c>
       <c r="G91">
         <v>1</v>
       </c>
       <c r="H91">
-        <v>39.99</v>
+        <v>119.99</v>
       </c>
       <c r="I91">
-        <v>22.39</v>
+        <v>57.99</v>
       </c>
       <c r="J91">
-        <v>5.69</v>
+        <v>12.46</v>
       </c>
       <c r="K91">
         <v>12</v>
       </c>
       <c r="L91">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N91">
-        <v>25.99</v>
+        <v>39.89</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -6502,22 +6532,22 @@
         <v>1</v>
       </c>
       <c r="Q91" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R91">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="S91">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="T91">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="U91">
         <v>0</v>
       </c>
       <c r="V91">
-        <v>157.21</v>
+        <v>64.98</v>
       </c>
     </row>
     <row r="92" spans="1:22">
@@ -6528,64 +6558,58 @@
         <v>41</v>
       </c>
       <c r="C92">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D92">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E92">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F92">
-        <v>318.34</v>
+        <v>72.39</v>
       </c>
       <c r="G92">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>279.97</v>
+        <v>0</v>
       </c>
       <c r="I92">
-        <v>126.67</v>
+        <v>0</v>
       </c>
       <c r="J92">
-        <v>31.08</v>
+        <v>0</v>
       </c>
       <c r="K92">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="L92">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N92">
-        <v>212.1</v>
+        <v>0</v>
       </c>
       <c r="O92">
         <v>0</v>
       </c>
       <c r="P92">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="R92">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>50</v>
       </c>
-      <c r="T92">
-        <v>6.8</v>
-      </c>
-      <c r="U92">
-        <v>0</v>
-      </c>
       <c r="V92">
-        <v>191.67</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="93" spans="1:22">
@@ -6596,64 +6620,64 @@
         <v>41</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E93">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F93">
-        <v>168.95</v>
+        <v>195.97</v>
       </c>
       <c r="G93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93">
-        <v>119.98</v>
+        <v>39.99</v>
       </c>
       <c r="I93">
-        <v>58.28</v>
+        <v>22.39</v>
       </c>
       <c r="J93">
-        <v>15</v>
+        <v>5.69</v>
       </c>
       <c r="K93">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="L93">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N93">
-        <v>66.77</v>
+        <v>25.99</v>
       </c>
       <c r="O93">
-        <v>24.78</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R93">
-        <v>40</v>
+        <v>14.3</v>
       </c>
       <c r="S93">
-        <v>20</v>
+        <v>42.9</v>
       </c>
       <c r="T93">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U93">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V93">
-        <v>110.67</v>
+        <v>173.58</v>
       </c>
     </row>
     <row r="94" spans="1:22">
@@ -6664,64 +6688,64 @@
         <v>41</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E94">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F94">
-        <v>26.3</v>
+        <v>318.34</v>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H94">
-        <v>34.99</v>
+        <v>279.97</v>
       </c>
       <c r="I94">
-        <v>12.31</v>
+        <v>126.67</v>
       </c>
       <c r="J94">
-        <v>6.53</v>
+        <v>31.08</v>
       </c>
       <c r="K94">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M94">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N94">
-        <v>33.42</v>
+        <v>212.1</v>
       </c>
       <c r="O94">
-        <v>33.42</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q94" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R94">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="S94">
         <v>50</v>
       </c>
       <c r="T94">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="U94">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V94">
-        <v>13.99</v>
+        <v>191.67</v>
       </c>
     </row>
     <row r="95" spans="1:22">
@@ -6732,64 +6756,64 @@
         <v>41</v>
       </c>
       <c r="C95">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E95">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F95">
-        <v>303.6</v>
+        <v>233.14</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95">
-        <v>40</v>
+        <v>119.98</v>
       </c>
       <c r="I95">
-        <v>23.46</v>
+        <v>58.28</v>
       </c>
       <c r="J95">
-        <v>8.58</v>
+        <v>15</v>
       </c>
       <c r="K95">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="L95">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M95">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N95">
-        <v>24.7</v>
+        <v>106.74</v>
       </c>
       <c r="O95">
-        <v>24.7</v>
+        <v>64.75</v>
       </c>
       <c r="P95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q95" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="R95">
-        <v>9.1</v>
+        <v>28.6</v>
       </c>
       <c r="S95">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="T95">
-        <v>2.9</v>
+        <v>7.1</v>
       </c>
       <c r="U95">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="V95">
-        <v>280.14</v>
+        <v>174.86</v>
       </c>
     </row>
     <row r="96" spans="1:22">
@@ -6800,58 +6824,64 @@
         <v>41</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E96">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F96">
-        <v>128.04</v>
+        <v>26.3</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>34.99</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>12.31</v>
       </c>
       <c r="J96">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="K96">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N96">
-        <v>26.09</v>
+        <v>33.42</v>
       </c>
       <c r="O96">
-        <v>26.09</v>
+        <v>33.42</v>
       </c>
       <c r="P96">
         <v>1</v>
       </c>
       <c r="Q96" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S96">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="T96">
+        <v>5.1</v>
+      </c>
+      <c r="U96">
+        <v>5.1</v>
       </c>
       <c r="V96">
-        <v>128.04</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="97" spans="1:22">
@@ -6862,58 +6892,64 @@
         <v>41</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D97">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E97">
+        <v>13</v>
+      </c>
+      <c r="F97">
+        <v>363.58</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>40</v>
+      </c>
+      <c r="I97">
+        <v>23.46</v>
+      </c>
+      <c r="J97">
+        <v>8.58</v>
+      </c>
+      <c r="K97">
         <v>8</v>
       </c>
-      <c r="F97">
-        <v>243.32</v>
-      </c>
-      <c r="G97">
-        <v>0</v>
-      </c>
-      <c r="H97">
-        <v>0</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="J97">
-        <v>0</v>
-      </c>
-      <c r="K97">
-        <v>1</v>
-      </c>
       <c r="L97">
         <v>1</v>
       </c>
       <c r="M97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="S97">
-        <v>14.3</v>
+        <v>41.7</v>
+      </c>
+      <c r="T97">
+        <v>2.9</v>
+      </c>
+      <c r="U97">
+        <v>2.9</v>
       </c>
       <c r="V97">
-        <v>243.32</v>
+        <v>340.12</v>
       </c>
     </row>
     <row r="98" spans="1:22">
@@ -6921,19 +6957,19 @@
         <v>24</v>
       </c>
       <c r="B98" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F98">
-        <v>32.99</v>
+        <v>137.83</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -6948,34 +6984,34 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>26.09</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>26.09</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="R98">
         <v>0</v>
       </c>
       <c r="S98">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="V98">
-        <v>32.99</v>
+        <v>137.83</v>
       </c>
     </row>
     <row r="99" spans="1:22">
@@ -6983,40 +7019,40 @@
         <v>24</v>
       </c>
       <c r="B99" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E99">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F99">
-        <v>83.98</v>
+        <v>243.32</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>39.99</v>
+        <v>0</v>
       </c>
       <c r="I99">
-        <v>25.99</v>
+        <v>0</v>
       </c>
       <c r="J99">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="K99">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="L99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N99">
         <v>0</v>
@@ -7028,22 +7064,16 @@
         <v>0</v>
       </c>
       <c r="Q99" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="R99">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S99">
-        <v>100</v>
-      </c>
-      <c r="T99">
-        <v>0</v>
-      </c>
-      <c r="U99">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="V99">
-        <v>57.99</v>
+        <v>243.32</v>
       </c>
     </row>
     <row r="100" spans="1:22">
@@ -7063,22 +7093,22 @@
         <v>1</v>
       </c>
       <c r="F100">
-        <v>41.99</v>
+        <v>32.99</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>119.99</v>
+        <v>0</v>
       </c>
       <c r="I100">
-        <v>41.99</v>
+        <v>0</v>
       </c>
       <c r="J100">
-        <v>12.46</v>
+        <v>0</v>
       </c>
       <c r="K100">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -7087,31 +7117,25 @@
         <v>1</v>
       </c>
       <c r="N100">
-        <v>48.1</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>48.1</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="R100">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S100">
         <v>100</v>
       </c>
-      <c r="T100">
-        <v>3.9</v>
-      </c>
-      <c r="U100">
-        <v>3.9</v>
-      </c>
       <c r="V100">
-        <v>0</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="101" spans="1:22">
@@ -7122,64 +7146,64 @@
         <v>42</v>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F101">
-        <v>86.25</v>
+        <v>83.98</v>
       </c>
       <c r="G101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H101">
-        <v>59.98</v>
+        <v>39.99</v>
       </c>
       <c r="I101">
-        <v>41.27</v>
+        <v>25.99</v>
       </c>
       <c r="J101">
-        <v>12.37</v>
+        <v>5.69</v>
       </c>
       <c r="K101">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="L101">
         <v>2</v>
       </c>
       <c r="M101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N101">
-        <v>23.59</v>
+        <v>0</v>
       </c>
       <c r="O101">
         <v>0</v>
       </c>
       <c r="P101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R101">
         <v>50</v>
       </c>
       <c r="S101">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T101">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U101">
         <v>0</v>
       </c>
       <c r="V101">
-        <v>44.98</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="102" spans="1:22">
@@ -7190,64 +7214,64 @@
         <v>42</v>
       </c>
       <c r="C102">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E102">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F102">
-        <v>146.11</v>
+        <v>41.99</v>
       </c>
       <c r="G102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H102">
-        <v>199.97</v>
+        <v>119.99</v>
       </c>
       <c r="I102">
-        <v>97.06999999999999</v>
+        <v>41.99</v>
       </c>
       <c r="J102">
-        <v>23.84</v>
+        <v>12.46</v>
       </c>
       <c r="K102">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102">
+        <v>48.1</v>
+      </c>
+      <c r="O102">
+        <v>48.1</v>
+      </c>
+      <c r="P102">
+        <v>2</v>
+      </c>
+      <c r="Q102" t="s">
         <v>53</v>
       </c>
-      <c r="M102">
-        <v>5</v>
-      </c>
-      <c r="N102">
-        <v>388</v>
-      </c>
-      <c r="O102">
-        <v>64.72</v>
-      </c>
-      <c r="P102">
-        <v>9</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>55</v>
-      </c>
       <c r="R102">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="S102">
         <v>100</v>
       </c>
       <c r="T102">
-        <v>16.3</v>
+        <v>3.9</v>
       </c>
       <c r="U102">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="V102">
-        <v>49.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:22">
@@ -7258,64 +7282,64 @@
         <v>42</v>
       </c>
       <c r="C103">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D103">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E103">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F103">
-        <v>287.51</v>
+        <v>86.25</v>
       </c>
       <c r="G103">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H103">
-        <v>359.95</v>
+        <v>59.98</v>
       </c>
       <c r="I103">
-        <v>161.75</v>
+        <v>41.27</v>
       </c>
       <c r="J103">
-        <v>47.95</v>
+        <v>12.37</v>
       </c>
       <c r="K103">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="L103">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="M103">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N103">
-        <v>87.98</v>
+        <v>23.59</v>
       </c>
       <c r="O103">
-        <v>45.99</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q103" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R103">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="S103">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="T103">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="U103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V103">
-        <v>125.76</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="104" spans="1:22">
@@ -7329,61 +7353,61 @@
         <v>5</v>
       </c>
       <c r="D104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E104">
         <v>5</v>
       </c>
       <c r="F104">
-        <v>132.43</v>
+        <v>146.11</v>
       </c>
       <c r="G104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H104">
-        <v>319.96</v>
+        <v>199.97</v>
       </c>
       <c r="I104">
-        <v>123.44</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="J104">
-        <v>22.85</v>
+        <v>23.84</v>
       </c>
       <c r="K104">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="L104">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="M104">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N104">
-        <v>20.02</v>
+        <v>388</v>
       </c>
       <c r="O104">
-        <v>20.02</v>
+        <v>64.72</v>
       </c>
       <c r="P104">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q104" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R104">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="S104">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T104">
-        <v>0.9</v>
+        <v>16.3</v>
       </c>
       <c r="U104">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="V104">
-        <v>8.99</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="105" spans="1:22">
@@ -7394,64 +7418,64 @@
         <v>42</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D105">
         <v>8</v>
       </c>
       <c r="E105">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F105">
-        <v>184.1</v>
+        <v>287.51</v>
       </c>
       <c r="G105">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H105">
-        <v>80</v>
+        <v>359.95</v>
       </c>
       <c r="I105">
-        <v>37.72</v>
+        <v>161.75</v>
       </c>
       <c r="J105">
-        <v>26.13</v>
+        <v>47.95</v>
       </c>
       <c r="K105">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="L105">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="M105">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N105">
-        <v>40.36</v>
+        <v>87.98</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>45.99</v>
       </c>
       <c r="P105">
         <v>2</v>
       </c>
       <c r="Q105" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="R105">
-        <v>30</v>
+        <v>55.6</v>
       </c>
       <c r="S105">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="T105">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V105">
-        <v>146.38</v>
+        <v>125.76</v>
       </c>
     </row>
     <row r="106" spans="1:22">
@@ -7465,61 +7489,61 @@
         <v>5</v>
       </c>
       <c r="D106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E106">
         <v>5</v>
       </c>
       <c r="F106">
-        <v>113.66</v>
+        <v>132.43</v>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H106">
-        <v>119.99</v>
+        <v>319.96</v>
       </c>
       <c r="I106">
-        <v>48.63</v>
+        <v>123.44</v>
       </c>
       <c r="J106">
-        <v>5.69</v>
+        <v>22.85</v>
       </c>
       <c r="K106">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L106">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>20.02</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>20.02</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q106" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R106">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="S106">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="V106">
-        <v>65.03</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="107" spans="1:22">
@@ -7530,58 +7554,64 @@
         <v>42</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E107">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F107">
-        <v>64.70999999999999</v>
+        <v>184.1</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>37.72</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>26.13</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>40.36</v>
       </c>
       <c r="O107">
         <v>0</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q107" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S107">
+        <v>75</v>
+      </c>
+      <c r="T107">
+        <v>1.5</v>
+      </c>
+      <c r="U107">
         <v>0</v>
       </c>
       <c r="V107">
-        <v>64.70999999999999</v>
+        <v>146.38</v>
       </c>
     </row>
     <row r="108" spans="1:22">
@@ -7589,61 +7619,67 @@
         <v>24</v>
       </c>
       <c r="B108" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E108">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F108">
-        <v>82.97</v>
+        <v>173.48</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>119.99</v>
       </c>
       <c r="I108">
-        <v>0</v>
+        <v>48.63</v>
       </c>
       <c r="J108">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="K108">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L108">
         <v>0</v>
       </c>
       <c r="M108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N108">
-        <v>125.08</v>
+        <v>112.93</v>
       </c>
       <c r="O108">
-        <v>125.08</v>
+        <v>112.93</v>
       </c>
       <c r="P108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q108" t="s">
+        <v>60</v>
+      </c>
+      <c r="R108">
+        <v>16.7</v>
+      </c>
+      <c r="S108">
         <v>50</v>
       </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108">
-        <v>100</v>
+      <c r="T108">
+        <v>19.8</v>
+      </c>
+      <c r="U108">
+        <v>19.8</v>
       </c>
       <c r="V108">
-        <v>82.97</v>
+        <v>124.85</v>
       </c>
     </row>
     <row r="109" spans="1:22">
@@ -7651,67 +7687,61 @@
         <v>24</v>
       </c>
       <c r="B109" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E109">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F109">
-        <v>82.98</v>
+        <v>118.06</v>
       </c>
       <c r="G109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>159.98</v>
+        <v>0</v>
       </c>
       <c r="I109">
-        <v>82.98</v>
+        <v>0</v>
       </c>
       <c r="J109">
-        <v>18.15</v>
+        <v>0</v>
       </c>
       <c r="K109">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L109">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N109">
-        <v>385.57</v>
+        <v>0</v>
       </c>
       <c r="O109">
         <v>0</v>
       </c>
       <c r="P109">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="R109">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S109">
-        <v>100</v>
-      </c>
-      <c r="T109">
-        <v>21.2</v>
-      </c>
-      <c r="U109">
         <v>0</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>118.06</v>
       </c>
     </row>
     <row r="110" spans="1:22">
@@ -7722,64 +7752,58 @@
         <v>43</v>
       </c>
       <c r="C110">
+        <v>2</v>
+      </c>
+      <c r="D110">
+        <v>2</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="F110">
+        <v>82.97</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>8</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>2</v>
+      </c>
+      <c r="N110">
+        <v>125.08</v>
+      </c>
+      <c r="O110">
+        <v>125.08</v>
+      </c>
+      <c r="P110">
         <v>3</v>
       </c>
-      <c r="D110">
-        <v>3</v>
-      </c>
-      <c r="E110">
-        <v>3</v>
-      </c>
-      <c r="F110">
-        <v>62.46</v>
-      </c>
-      <c r="G110">
-        <v>2</v>
-      </c>
-      <c r="H110">
-        <v>59.98</v>
-      </c>
-      <c r="I110">
-        <v>44.97</v>
-      </c>
-      <c r="J110">
-        <v>12.37</v>
-      </c>
-      <c r="K110">
-        <v>12</v>
-      </c>
-      <c r="L110">
-        <v>12</v>
-      </c>
-      <c r="M110">
-        <v>3</v>
-      </c>
-      <c r="N110">
-        <v>4148</v>
-      </c>
-      <c r="O110">
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <v>130</v>
-      </c>
       <c r="Q110" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R110">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="S110">
         <v>100</v>
       </c>
-      <c r="T110">
-        <v>335.3</v>
-      </c>
-      <c r="U110">
-        <v>0</v>
-      </c>
       <c r="V110">
-        <v>17.49</v>
+        <v>82.97</v>
       </c>
     </row>
     <row r="111" spans="1:22">
@@ -7790,64 +7814,64 @@
         <v>43</v>
       </c>
       <c r="C111">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E111">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F111">
-        <v>186.1</v>
+        <v>82.98</v>
       </c>
       <c r="G111">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H111">
-        <v>319.96</v>
+        <v>159.98</v>
       </c>
       <c r="I111">
-        <v>132.44</v>
+        <v>82.98</v>
       </c>
       <c r="J111">
-        <v>37.46</v>
+        <v>18.15</v>
       </c>
       <c r="K111">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="L111">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="M111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N111">
-        <v>741.95</v>
+        <v>385.57</v>
       </c>
       <c r="O111">
-        <v>468.85</v>
+        <v>0</v>
       </c>
       <c r="P111">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="Q111" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R111">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="S111">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="T111">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="U111">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="V111">
-        <v>53.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:22">
@@ -7858,64 +7882,64 @@
         <v>43</v>
       </c>
       <c r="C112">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D112">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E112">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F112">
-        <v>214.08</v>
+        <v>62.46</v>
       </c>
       <c r="G112">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H112">
-        <v>359.96</v>
+        <v>59.98</v>
       </c>
       <c r="I112">
-        <v>159.05</v>
+        <v>44.97</v>
       </c>
       <c r="J112">
-        <v>40.39</v>
+        <v>12.37</v>
       </c>
       <c r="K112">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="L112">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="M112">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N112">
-        <v>347.11</v>
+        <v>4148</v>
       </c>
       <c r="O112">
         <v>0</v>
       </c>
       <c r="P112">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="Q112" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R112">
         <v>66.7</v>
       </c>
       <c r="S112">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="T112">
-        <v>8.6</v>
+        <v>335.3</v>
       </c>
       <c r="U112">
         <v>0</v>
       </c>
       <c r="V112">
-        <v>55.03</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="113" spans="1:22">
@@ -7926,64 +7950,64 @@
         <v>43</v>
       </c>
       <c r="C113">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D113">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E113">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F113">
-        <v>278.56</v>
+        <v>246.09</v>
       </c>
       <c r="G113">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H113">
-        <v>519.9299999999999</v>
+        <v>319.96</v>
       </c>
       <c r="I113">
-        <v>221.57</v>
+        <v>132.44</v>
       </c>
       <c r="J113">
-        <v>60.56</v>
+        <v>37.46</v>
       </c>
       <c r="K113">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="L113">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="M113">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N113">
-        <v>1246.25</v>
+        <v>741.95</v>
       </c>
       <c r="O113">
-        <v>657.13</v>
+        <v>468.85</v>
       </c>
       <c r="P113">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="Q113" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="R113">
-        <v>87.5</v>
+        <v>57.1</v>
       </c>
       <c r="S113">
-        <v>87.5</v>
+        <v>50</v>
       </c>
       <c r="T113">
-        <v>20.6</v>
+        <v>19.8</v>
       </c>
       <c r="U113">
-        <v>10.9</v>
+        <v>12.5</v>
       </c>
       <c r="V113">
-        <v>56.99</v>
+        <v>113.65</v>
       </c>
     </row>
     <row r="114" spans="1:22">
@@ -7994,64 +8018,64 @@
         <v>43</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D114">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E114">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F114">
-        <v>293.78</v>
+        <v>214.08</v>
       </c>
       <c r="G114">
         <v>4</v>
       </c>
       <c r="H114">
-        <v>479.96</v>
+        <v>359.96</v>
       </c>
       <c r="I114">
-        <v>189.58</v>
+        <v>159.05</v>
       </c>
       <c r="J114">
-        <v>50.55</v>
+        <v>40.39</v>
       </c>
       <c r="K114">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="L114">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="M114">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N114">
-        <v>635.74</v>
+        <v>347.11</v>
       </c>
       <c r="O114">
-        <v>496.06</v>
+        <v>0</v>
       </c>
       <c r="P114">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q114" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R114">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="S114">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="T114">
-        <v>12.6</v>
+        <v>8.6</v>
       </c>
       <c r="U114">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="V114">
-        <v>104.2</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="115" spans="1:22">
@@ -8062,64 +8086,64 @@
         <v>43</v>
       </c>
       <c r="C115">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D115">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E115">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F115">
-        <v>42.97</v>
+        <v>278.56</v>
       </c>
       <c r="G115">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H115">
-        <v>94.98</v>
+        <v>519.9299999999999</v>
       </c>
       <c r="I115">
-        <v>42.97</v>
+        <v>221.57</v>
       </c>
       <c r="J115">
-        <v>20.36</v>
+        <v>60.56</v>
       </c>
       <c r="K115">
+        <v>58</v>
+      </c>
+      <c r="L115">
+        <v>38</v>
+      </c>
+      <c r="M115">
         <v>7</v>
       </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115">
-        <v>3</v>
-      </c>
       <c r="N115">
-        <v>102.99</v>
+        <v>1246.25</v>
       </c>
       <c r="O115">
-        <v>102.99</v>
+        <v>657.13</v>
       </c>
       <c r="P115">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="Q115" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R115">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="S115">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="T115">
-        <v>5.1</v>
+        <v>20.6</v>
       </c>
       <c r="U115">
-        <v>5.1</v>
+        <v>10.9</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="116" spans="1:22">
@@ -8130,58 +8154,64 @@
         <v>43</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E116">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F116">
-        <v>14.99</v>
+        <v>293.78</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>479.96</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>189.58</v>
       </c>
       <c r="J116">
-        <v>0</v>
+        <v>50.55</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L116">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M116">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>635.74</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>496.06</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q116" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>85.7</v>
+      </c>
+      <c r="T116">
+        <v>12.6</v>
+      </c>
+      <c r="U116">
+        <v>9.800000000000001</v>
       </c>
       <c r="V116">
-        <v>14.99</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="117" spans="1:22">
@@ -8192,64 +8222,64 @@
         <v>43</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D117">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E117">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F117">
-        <v>176.17</v>
+        <v>42.97</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H117">
-        <v>119.99</v>
+        <v>94.98</v>
       </c>
       <c r="I117">
-        <v>51.77</v>
+        <v>42.97</v>
       </c>
       <c r="J117">
-        <v>5.69</v>
+        <v>20.36</v>
       </c>
       <c r="K117">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L117">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M117">
         <v>3</v>
       </c>
       <c r="N117">
-        <v>180.1</v>
+        <v>102.99</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>102.99</v>
       </c>
       <c r="P117">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q117" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R117">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="S117">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T117">
-        <v>31.7</v>
+        <v>5.1</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V117">
-        <v>124.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:22">
@@ -8260,16 +8290,16 @@
         <v>43</v>
       </c>
       <c r="C118">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E118">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F118">
-        <v>180.61</v>
+        <v>14.99</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -8284,34 +8314,34 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L118">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>59.99</v>
+        <v>0</v>
       </c>
       <c r="O118">
         <v>0</v>
       </c>
       <c r="P118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="R118">
         <v>0</v>
       </c>
       <c r="S118">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V118">
-        <v>180.61</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="119" spans="1:22">
@@ -8319,67 +8349,67 @@
         <v>24</v>
       </c>
       <c r="B119" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D119">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F119">
-        <v>47.58</v>
+        <v>216.15</v>
       </c>
       <c r="G119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H119">
-        <v>79.98</v>
+        <v>119.99</v>
       </c>
       <c r="I119">
-        <v>47.58</v>
+        <v>51.77</v>
       </c>
       <c r="J119">
-        <v>11.38</v>
+        <v>5.69</v>
       </c>
       <c r="K119">
+        <v>12</v>
+      </c>
+      <c r="L119">
+        <v>4</v>
+      </c>
+      <c r="M119">
+        <v>5</v>
+      </c>
+      <c r="N119">
+        <v>180.1</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
         <v>3</v>
       </c>
-      <c r="L119">
-        <v>3</v>
-      </c>
-      <c r="M119">
-        <v>2</v>
-      </c>
-      <c r="N119">
-        <v>25.82</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>1</v>
-      </c>
       <c r="Q119" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="R119">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="S119">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="T119">
-        <v>2.3</v>
+        <v>31.7</v>
       </c>
       <c r="U119">
         <v>0</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>164.38</v>
       </c>
     </row>
     <row r="120" spans="1:22">
@@ -8387,19 +8417,19 @@
         <v>24</v>
       </c>
       <c r="B120" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F120">
-        <v>22.79</v>
+        <v>127.26</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -8414,34 +8444,34 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L120">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>59.99</v>
       </c>
       <c r="O120">
         <v>0</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q120" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="R120">
         <v>0</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V120">
-        <v>22.79</v>
+        <v>127.26</v>
       </c>
     </row>
     <row r="121" spans="1:22">
@@ -8461,7 +8491,7 @@
         <v>2</v>
       </c>
       <c r="F121">
-        <v>50.68</v>
+        <v>47.58</v>
       </c>
       <c r="G121">
         <v>2</v>
@@ -8470,31 +8500,31 @@
         <v>79.98</v>
       </c>
       <c r="I121">
-        <v>50.68</v>
+        <v>47.58</v>
       </c>
       <c r="J121">
         <v>11.38</v>
       </c>
       <c r="K121">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="L121">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="M121">
         <v>2</v>
       </c>
       <c r="N121">
-        <v>4455.91</v>
+        <v>25.82</v>
       </c>
       <c r="O121">
-        <v>277.62</v>
+        <v>0</v>
       </c>
       <c r="P121">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="Q121" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R121">
         <v>100</v>
@@ -8503,10 +8533,10 @@
         <v>100</v>
       </c>
       <c r="T121">
-        <v>391.6</v>
+        <v>2.3</v>
       </c>
       <c r="U121">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="V121">
         <v>0</v>
@@ -8529,7 +8559,7 @@
         <v>1</v>
       </c>
       <c r="F122">
-        <v>9.390000000000001</v>
+        <v>22.79</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -8562,7 +8592,7 @@
         <v>0</v>
       </c>
       <c r="Q122" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -8571,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="V122">
-        <v>9.390000000000001</v>
+        <v>22.79</v>
       </c>
     </row>
     <row r="123" spans="1:22">
@@ -8582,58 +8612,64 @@
         <v>44</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123">
-        <v>18.19</v>
+        <v>50.68</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>79.98</v>
       </c>
       <c r="I123">
-        <v>0</v>
+        <v>50.68</v>
       </c>
       <c r="J123">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="K123">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="L123">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="M123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>4456.14</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>277.62</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="Q123" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S123">
         <v>100</v>
       </c>
+      <c r="T123">
+        <v>391.6</v>
+      </c>
+      <c r="U123">
+        <v>24.4</v>
+      </c>
       <c r="V123">
-        <v>18.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:22">
@@ -8653,7 +8689,7 @@
         <v>1</v>
       </c>
       <c r="F124">
-        <v>11.97</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -8668,13 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L124">
         <v>0</v>
       </c>
       <c r="M124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N124">
         <v>0</v>
@@ -8686,16 +8722,16 @@
         <v>0</v>
       </c>
       <c r="Q124" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R124">
         <v>0</v>
       </c>
       <c r="S124">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V124">
-        <v>11.97</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="125" spans="1:22">
@@ -8703,67 +8739,61 @@
         <v>24</v>
       </c>
       <c r="B125" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125">
-        <v>48.97</v>
+        <v>18.19</v>
       </c>
       <c r="G125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>79.98</v>
+        <v>0</v>
       </c>
       <c r="I125">
-        <v>48.97</v>
+        <v>0</v>
       </c>
       <c r="J125">
-        <v>11.38</v>
+        <v>0</v>
       </c>
       <c r="K125">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125">
         <v>1</v>
       </c>
       <c r="N125">
-        <v>1044.63</v>
+        <v>0</v>
       </c>
       <c r="O125">
-        <v>1044.63</v>
+        <v>0</v>
       </c>
       <c r="P125">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="R125">
+        <v>0</v>
+      </c>
+      <c r="S125">
         <v>100</v>
       </c>
-      <c r="S125">
-        <v>50</v>
-      </c>
-      <c r="T125">
-        <v>91.8</v>
-      </c>
-      <c r="U125">
-        <v>91.8</v>
-      </c>
       <c r="V125">
-        <v>0</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="126" spans="1:22">
@@ -8771,7 +8801,7 @@
         <v>24</v>
       </c>
       <c r="B126" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -8783,28 +8813,28 @@
         <v>1</v>
       </c>
       <c r="F126">
-        <v>27.98</v>
+        <v>11.97</v>
       </c>
       <c r="G126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>39.99</v>
+        <v>0</v>
       </c>
       <c r="I126">
-        <v>27.98</v>
+        <v>0</v>
       </c>
       <c r="J126">
-        <v>10.71</v>
+        <v>0</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L126">
         <v>0</v>
       </c>
       <c r="M126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N126">
         <v>0</v>
@@ -8816,22 +8846,16 @@
         <v>0</v>
       </c>
       <c r="Q126" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="R126">
+        <v>0</v>
+      </c>
+      <c r="S126">
         <v>100</v>
       </c>
-      <c r="S126">
-        <v>0</v>
-      </c>
-      <c r="T126">
-        <v>0</v>
-      </c>
-      <c r="U126">
-        <v>0</v>
-      </c>
       <c r="V126">
-        <v>0</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="127" spans="1:22">
@@ -8842,61 +8866,61 @@
         <v>45</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127">
-        <v>20.39</v>
+        <v>48.97</v>
       </c>
       <c r="G127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H127">
-        <v>39.99</v>
+        <v>79.98</v>
       </c>
       <c r="I127">
-        <v>20.39</v>
+        <v>48.97</v>
       </c>
       <c r="J127">
-        <v>5.69</v>
+        <v>11.38</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L127">
         <v>0</v>
       </c>
       <c r="M127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1044.63</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>1044.63</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q127" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R127">
         <v>100</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="V127">
         <v>0</v>
@@ -8910,16 +8934,16 @@
         <v>45</v>
       </c>
       <c r="C128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128">
-        <v>63.78</v>
+        <v>27.98</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -8928,19 +8952,19 @@
         <v>39.99</v>
       </c>
       <c r="I128">
-        <v>25.99</v>
+        <v>27.98</v>
       </c>
       <c r="J128">
-        <v>5.69</v>
+        <v>10.71</v>
       </c>
       <c r="K128">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L128">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M128">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N128">
         <v>0</v>
@@ -8952,13 +8976,13 @@
         <v>0</v>
       </c>
       <c r="Q128" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R128">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S128">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T128">
         <v>0</v>
@@ -8967,7 +8991,7 @@
         <v>0</v>
       </c>
       <c r="V128">
-        <v>37.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:22">
@@ -8978,28 +9002,28 @@
         <v>45</v>
       </c>
       <c r="C129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129">
-        <v>24.17</v>
+        <v>20.39</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>39.99</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>20.39</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -9020,16 +9044,22 @@
         <v>0</v>
       </c>
       <c r="Q129" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S129">
         <v>0</v>
       </c>
+      <c r="T129">
+        <v>0</v>
+      </c>
+      <c r="U129">
+        <v>0</v>
+      </c>
       <c r="V129">
-        <v>24.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:22">
@@ -9037,67 +9067,67 @@
         <v>24</v>
       </c>
       <c r="B130" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130">
-        <v>29.39</v>
+        <v>63.78</v>
       </c>
       <c r="G130">
         <v>1</v>
       </c>
       <c r="H130">
-        <v>79.98999999999999</v>
+        <v>39.99</v>
       </c>
       <c r="I130">
-        <v>29.39</v>
+        <v>25.99</v>
       </c>
       <c r="J130">
-        <v>9.31</v>
+        <v>5.69</v>
       </c>
       <c r="K130">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="L130">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="M130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N130">
-        <v>2676.61</v>
+        <v>0</v>
       </c>
       <c r="O130">
         <v>0</v>
       </c>
       <c r="P130">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="R130">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="S130">
         <v>100</v>
       </c>
       <c r="T130">
-        <v>287.5</v>
+        <v>0</v>
       </c>
       <c r="U130">
         <v>0</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="131" spans="1:22">
@@ -9105,19 +9135,19 @@
         <v>24</v>
       </c>
       <c r="B131" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131">
-        <v>29.98</v>
+        <v>24.17</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -9132,13 +9162,13 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="M131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N131">
         <v>0</v>
@@ -9150,16 +9180,16 @@
         <v>0</v>
       </c>
       <c r="Q131" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R131">
         <v>0</v>
       </c>
       <c r="S131">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V131">
-        <v>29.98</v>
+        <v>24.17</v>
       </c>
     </row>
     <row r="132" spans="1:22">
@@ -9179,40 +9209,40 @@
         <v>1</v>
       </c>
       <c r="F132">
-        <v>19.49</v>
+        <v>29.39</v>
       </c>
       <c r="G132">
         <v>1</v>
       </c>
       <c r="H132">
-        <v>39.99</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="I132">
-        <v>19.49</v>
+        <v>29.39</v>
       </c>
       <c r="J132">
-        <v>5.69</v>
+        <v>9.31</v>
       </c>
       <c r="K132">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="L132">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M132">
         <v>1</v>
       </c>
       <c r="N132">
-        <v>217.61</v>
+        <v>2676.61</v>
       </c>
       <c r="O132">
-        <v>217.61</v>
+        <v>0</v>
       </c>
       <c r="P132">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="Q132" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="R132">
         <v>100</v>
@@ -9221,10 +9251,10 @@
         <v>100</v>
       </c>
       <c r="T132">
-        <v>38.2</v>
+        <v>287.5</v>
       </c>
       <c r="U132">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="V132">
         <v>0</v>
@@ -9247,22 +9277,22 @@
         <v>1</v>
       </c>
       <c r="F133">
-        <v>21.37</v>
+        <v>29.98</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133">
-        <v>39.99</v>
+        <v>0</v>
       </c>
       <c r="I133">
-        <v>21.37</v>
+        <v>0</v>
       </c>
       <c r="J133">
-        <v>6.53</v>
+        <v>0</v>
       </c>
       <c r="K133">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -9271,31 +9301,25 @@
         <v>1</v>
       </c>
       <c r="N133">
-        <v>341.16</v>
+        <v>0</v>
       </c>
       <c r="O133">
-        <v>341.16</v>
+        <v>0</v>
       </c>
       <c r="P133">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R133">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S133">
         <v>100</v>
       </c>
-      <c r="T133">
-        <v>52.2</v>
-      </c>
-      <c r="U133">
-        <v>52.2</v>
-      </c>
       <c r="V133">
-        <v>0</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="134" spans="1:22">
@@ -9303,7 +9327,7 @@
         <v>24</v>
       </c>
       <c r="B134" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -9315,7 +9339,7 @@
         <v>1</v>
       </c>
       <c r="F134">
-        <v>22.99</v>
+        <v>19.49</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -9324,13 +9348,13 @@
         <v>39.99</v>
       </c>
       <c r="I134">
-        <v>22.99</v>
+        <v>19.49</v>
       </c>
       <c r="J134">
-        <v>5.64</v>
+        <v>5.69</v>
       </c>
       <c r="K134">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="L134">
         <v>0</v>
@@ -9339,16 +9363,16 @@
         <v>1</v>
       </c>
       <c r="N134">
-        <v>840.29</v>
+        <v>217.61</v>
       </c>
       <c r="O134">
-        <v>840.29</v>
+        <v>217.61</v>
       </c>
       <c r="P134">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Q134" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="R134">
         <v>100</v>
@@ -9357,10 +9381,10 @@
         <v>100</v>
       </c>
       <c r="T134">
-        <v>149</v>
+        <v>38.2</v>
       </c>
       <c r="U134">
-        <v>149</v>
+        <v>38.2</v>
       </c>
       <c r="V134">
         <v>0</v>
@@ -9371,7 +9395,7 @@
         <v>24</v>
       </c>
       <c r="B135" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -9383,52 +9407,52 @@
         <v>1</v>
       </c>
       <c r="F135">
-        <v>31.99</v>
+        <v>21.37</v>
       </c>
       <c r="G135">
         <v>1</v>
       </c>
       <c r="H135">
-        <v>79.98999999999999</v>
+        <v>39.99</v>
       </c>
       <c r="I135">
-        <v>31.99</v>
+        <v>21.37</v>
       </c>
       <c r="J135">
-        <v>9.31</v>
+        <v>6.53</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
       <c r="M135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>341.16</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>341.16</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q135" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R135">
         <v>100</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>52.2</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>52.2</v>
       </c>
       <c r="V135">
         <v>0</v>
@@ -9451,49 +9475,55 @@
         <v>1</v>
       </c>
       <c r="F136">
-        <v>38.94</v>
+        <v>22.99</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>39.99</v>
       </c>
       <c r="I136">
-        <v>0</v>
+        <v>22.99</v>
       </c>
       <c r="J136">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
       <c r="M136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>840.29</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>840.29</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q136" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="T136">
+        <v>149</v>
+      </c>
+      <c r="U136">
+        <v>149</v>
       </c>
       <c r="V136">
-        <v>38.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:22">
@@ -9501,40 +9531,40 @@
         <v>24</v>
       </c>
       <c r="B137" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C137">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D137">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E137">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F137">
-        <v>155.73</v>
+        <v>31.99</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="I137">
-        <v>0</v>
+        <v>31.99</v>
       </c>
       <c r="J137">
-        <v>0</v>
+        <v>9.31</v>
       </c>
       <c r="K137">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L137">
         <v>0</v>
       </c>
       <c r="M137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N137">
         <v>0</v>
@@ -9546,16 +9576,22 @@
         <v>0</v>
       </c>
       <c r="Q137" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S137">
-        <v>16.7</v>
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
       </c>
       <c r="V137">
-        <v>155.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:22">
@@ -9563,19 +9599,19 @@
         <v>24</v>
       </c>
       <c r="B138" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D138">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E138">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F138">
-        <v>113.35</v>
+        <v>38.94</v>
       </c>
       <c r="G138">
         <v>0</v>
@@ -9590,13 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
       <c r="M138">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N138">
         <v>0</v>
@@ -9608,16 +9644,16 @@
         <v>0</v>
       </c>
       <c r="Q138" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="R138">
         <v>0</v>
       </c>
       <c r="S138">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V138">
-        <v>113.35</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="139" spans="1:22">
@@ -9628,64 +9664,58 @@
         <v>48</v>
       </c>
       <c r="C139">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D139">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E139">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F139">
-        <v>737.09</v>
+        <v>37.98</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>39.99</v>
+        <v>0</v>
       </c>
       <c r="I139">
-        <v>23.91</v>
+        <v>0</v>
       </c>
       <c r="J139">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="K139">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="M139">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N139">
-        <v>202.33</v>
+        <v>0</v>
       </c>
       <c r="O139">
-        <v>202.33</v>
+        <v>0</v>
       </c>
       <c r="P139">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R139">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S139">
-        <v>26.9</v>
-      </c>
-      <c r="T139">
-        <v>35.6</v>
-      </c>
-      <c r="U139">
-        <v>35.6</v>
+        <v>0</v>
       </c>
       <c r="V139">
-        <v>713.1799999999999</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="140" spans="1:22">
@@ -9696,64 +9726,58 @@
         <v>48</v>
       </c>
       <c r="C140">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="D140">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="E140">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="F140">
-        <v>3553.11</v>
+        <v>160.81</v>
       </c>
       <c r="G140">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H140">
-        <v>239.96</v>
+        <v>0</v>
       </c>
       <c r="I140">
-        <v>132.06</v>
+        <v>0</v>
       </c>
       <c r="J140">
-        <v>29.53</v>
+        <v>0</v>
       </c>
       <c r="K140">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
       <c r="M140">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N140">
-        <v>239.22</v>
+        <v>0</v>
       </c>
       <c r="O140">
-        <v>239.22</v>
+        <v>0</v>
       </c>
       <c r="P140">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R140">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S140">
-        <v>11.8</v>
-      </c>
-      <c r="T140">
-        <v>8.1</v>
-      </c>
-      <c r="U140">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="V140">
-        <v>3421.05</v>
+        <v>160.81</v>
       </c>
     </row>
     <row r="141" spans="1:22">
@@ -9764,64 +9788,58 @@
         <v>48</v>
       </c>
       <c r="C141">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="D141">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="E141">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="F141">
-        <v>7032.67</v>
+        <v>574.41</v>
       </c>
       <c r="G141">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>639.9</v>
+        <v>0</v>
       </c>
       <c r="I141">
-        <v>266.47</v>
+        <v>0</v>
       </c>
       <c r="J141">
-        <v>82.75</v>
+        <v>0</v>
       </c>
       <c r="K141">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
       <c r="M141">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="N141">
-        <v>231.85</v>
+        <v>0</v>
       </c>
       <c r="O141">
-        <v>231.85</v>
+        <v>0</v>
       </c>
       <c r="P141">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R141">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S141">
-        <v>7.2</v>
-      </c>
-      <c r="T141">
-        <v>2.8</v>
-      </c>
-      <c r="U141">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="V141">
-        <v>6766.2</v>
+        <v>574.41</v>
       </c>
     </row>
     <row r="142" spans="1:22">
@@ -9832,64 +9850,64 @@
         <v>48</v>
       </c>
       <c r="C142">
-        <v>380</v>
+        <v>47</v>
       </c>
       <c r="D142">
-        <v>375</v>
+        <v>47</v>
       </c>
       <c r="E142">
-        <v>380</v>
+        <v>47</v>
       </c>
       <c r="F142">
-        <v>10991.64</v>
+        <v>1355.93</v>
       </c>
       <c r="G142">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H142">
-        <v>1399.78</v>
+        <v>79.98</v>
       </c>
       <c r="I142">
-        <v>620.36</v>
+        <v>51.58</v>
       </c>
       <c r="J142">
-        <v>175.47</v>
+        <v>16.4</v>
       </c>
       <c r="K142">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
       <c r="M142">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N142">
-        <v>224.85</v>
+        <v>0</v>
       </c>
       <c r="O142">
-        <v>224.85</v>
+        <v>0</v>
       </c>
       <c r="P142">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R142">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="S142">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="T142">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U142">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V142">
-        <v>10371.28</v>
+        <v>1304.35</v>
       </c>
     </row>
     <row r="143" spans="1:22">
@@ -9900,64 +9918,64 @@
         <v>48</v>
       </c>
       <c r="C143">
-        <v>298</v>
+        <v>58</v>
       </c>
       <c r="D143">
-        <v>295</v>
+        <v>56</v>
       </c>
       <c r="E143">
-        <v>298</v>
+        <v>58</v>
       </c>
       <c r="F143">
-        <v>9254.49</v>
+        <v>1806.25</v>
       </c>
       <c r="G143">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H143">
-        <v>1299.81</v>
+        <v>239.95</v>
       </c>
       <c r="I143">
-        <v>569.36</v>
+        <v>124.57</v>
       </c>
       <c r="J143">
-        <v>160.75</v>
+        <v>37.09</v>
       </c>
       <c r="K143">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L143">
         <v>0</v>
       </c>
       <c r="M143">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N143">
-        <v>138.48</v>
+        <v>0</v>
       </c>
       <c r="O143">
-        <v>138.48</v>
+        <v>0</v>
       </c>
       <c r="P143">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R143">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="S143">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="T143">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="U143">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="V143">
-        <v>8685.129999999999</v>
+        <v>1681.68</v>
       </c>
     </row>
     <row r="144" spans="1:22">
@@ -9968,37 +9986,37 @@
         <v>48</v>
       </c>
       <c r="C144">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D144">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E144">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F144">
-        <v>259.17</v>
+        <v>1293.21</v>
       </c>
       <c r="G144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H144">
-        <v>39.99</v>
+        <v>119.98</v>
       </c>
       <c r="I144">
-        <v>21.37</v>
+        <v>53.71</v>
       </c>
       <c r="J144">
-        <v>5.74</v>
+        <v>15</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L144">
         <v>0</v>
       </c>
       <c r="M144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N144">
         <v>0</v>
@@ -10010,13 +10028,13 @@
         <v>0</v>
       </c>
       <c r="Q144" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R144">
-        <v>9.1</v>
+        <v>4.9</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T144">
         <v>0</v>
@@ -10025,7 +10043,7 @@
         <v>0</v>
       </c>
       <c r="V144">
-        <v>237.8</v>
+        <v>1239.5</v>
       </c>
     </row>
     <row r="145" spans="1:22">
@@ -10036,64 +10054,64 @@
         <v>48</v>
       </c>
       <c r="C145">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="D145">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="E145">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="F145">
-        <v>2492.76</v>
+        <v>43.86</v>
       </c>
       <c r="G145">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H145">
-        <v>644.9</v>
+        <v>39.99</v>
       </c>
       <c r="I145">
-        <v>298.5</v>
+        <v>21.37</v>
       </c>
       <c r="J145">
-        <v>65.23999999999999</v>
+        <v>5.74</v>
       </c>
       <c r="K145">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L145">
         <v>0</v>
       </c>
       <c r="M145">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N145">
-        <v>14.24</v>
+        <v>0</v>
       </c>
       <c r="O145">
-        <v>14.24</v>
+        <v>0</v>
       </c>
       <c r="P145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R145">
-        <v>8.9</v>
+        <v>50</v>
       </c>
       <c r="S145">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T145">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="U145">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="V145">
-        <v>2194.26</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="146" spans="1:22">
@@ -10104,64 +10122,64 @@
         <v>48</v>
       </c>
       <c r="C146">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="D146">
-        <v>338</v>
+        <v>18</v>
       </c>
       <c r="E146">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="F146">
-        <v>6977.66</v>
+        <v>333.33</v>
       </c>
       <c r="G146">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H146">
-        <v>539.98</v>
+        <v>40</v>
       </c>
       <c r="I146">
-        <v>215.94</v>
+        <v>19.99</v>
       </c>
       <c r="J146">
-        <v>63.25</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="K146">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L146">
         <v>0</v>
       </c>
       <c r="M146">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N146">
-        <v>80.09</v>
+        <v>0</v>
       </c>
       <c r="O146">
-        <v>80.09</v>
+        <v>0</v>
       </c>
       <c r="P146">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R146">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="S146">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T146">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U146">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V146">
-        <v>6761.72</v>
+        <v>313.34</v>
       </c>
     </row>
     <row r="147" spans="1:22">
@@ -10172,64 +10190,58 @@
         <v>48</v>
       </c>
       <c r="C147">
-        <v>254</v>
+        <v>54</v>
       </c>
       <c r="D147">
-        <v>252</v>
+        <v>51</v>
       </c>
       <c r="E147">
-        <v>254</v>
+        <v>54</v>
       </c>
       <c r="F147">
-        <v>6012.6</v>
+        <v>1052.67</v>
       </c>
       <c r="G147">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>274.98</v>
+        <v>0</v>
       </c>
       <c r="I147">
-        <v>128.18</v>
+        <v>0</v>
       </c>
       <c r="J147">
-        <v>42.73</v>
+        <v>0</v>
       </c>
       <c r="K147">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L147">
         <v>0</v>
       </c>
       <c r="M147">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N147">
-        <v>137.62</v>
+        <v>0</v>
       </c>
       <c r="O147">
-        <v>137.62</v>
+        <v>0</v>
       </c>
       <c r="P147">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R147">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S147">
-        <v>2.8</v>
-      </c>
-      <c r="T147">
-        <v>3.2</v>
-      </c>
-      <c r="U147">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="V147">
-        <v>5884.42</v>
+        <v>1052.67</v>
       </c>
     </row>
     <row r="148" spans="1:22">
@@ -10240,37 +10252,37 @@
         <v>48</v>
       </c>
       <c r="C148">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="D148">
-        <v>191</v>
+        <v>41</v>
       </c>
       <c r="E148">
-        <v>205</v>
+        <v>41</v>
       </c>
       <c r="F148">
-        <v>5006.55</v>
+        <v>875.16</v>
       </c>
       <c r="G148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148">
-        <v>39.99</v>
+        <v>45</v>
       </c>
       <c r="I148">
-        <v>14.93</v>
+        <v>14.84</v>
       </c>
       <c r="J148">
-        <v>9.59</v>
+        <v>5.69</v>
       </c>
       <c r="K148">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L148">
         <v>0</v>
       </c>
       <c r="M148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N148">
         <v>0</v>
@@ -10282,13 +10294,13 @@
         <v>0</v>
       </c>
       <c r="Q148" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R148">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="S148">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="T148">
         <v>0</v>
@@ -10297,7 +10309,7 @@
         <v>0</v>
       </c>
       <c r="V148">
-        <v>4991.62</v>
+        <v>860.3200000000001</v>
       </c>
     </row>
     <row r="149" spans="1:22">
@@ -10305,31 +10317,31 @@
         <v>24</v>
       </c>
       <c r="B149" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E149">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F149">
-        <v>25.99</v>
+        <v>1070.4</v>
       </c>
       <c r="G149">
         <v>1</v>
       </c>
       <c r="H149">
-        <v>39.99</v>
+        <v>19.99</v>
       </c>
       <c r="I149">
-        <v>25.99</v>
+        <v>7.5</v>
       </c>
       <c r="J149">
-        <v>5.69</v>
+        <v>4.86</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -10350,10 +10362,10 @@
         <v>0</v>
       </c>
       <c r="Q149" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="R149">
-        <v>100</v>
+        <v>2.5</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -10365,7 +10377,7 @@
         <v>0</v>
       </c>
       <c r="V149">
-        <v>0</v>
+        <v>1062.9</v>
       </c>
     </row>
     <row r="150" spans="1:22">
@@ -10385,19 +10397,19 @@
         <v>1</v>
       </c>
       <c r="F150">
-        <v>22.49</v>
+        <v>25.99</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>39.99</v>
       </c>
       <c r="I150">
-        <v>0</v>
+        <v>25.99</v>
       </c>
       <c r="J150">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -10418,16 +10430,22 @@
         <v>0</v>
       </c>
       <c r="Q150" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S150">
         <v>0</v>
       </c>
+      <c r="T150">
+        <v>0</v>
+      </c>
+      <c r="U150">
+        <v>0</v>
+      </c>
       <c r="V150">
-        <v>22.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:22">
@@ -10447,7 +10465,7 @@
         <v>1</v>
       </c>
       <c r="F151">
-        <v>39.89</v>
+        <v>22.49</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -10480,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="Q151" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R151">
         <v>0</v>
@@ -10489,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="V151">
-        <v>39.89</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="152" spans="1:22">
@@ -10509,48 +10527,110 @@
         <v>1</v>
       </c>
       <c r="F152">
+        <v>39.89</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>59</v>
+      </c>
+      <c r="R152">
+        <v>0</v>
+      </c>
+      <c r="S152">
+        <v>0</v>
+      </c>
+      <c r="V152">
+        <v>39.89</v>
+      </c>
+    </row>
+    <row r="153" spans="1:22">
+      <c r="A153" t="s">
+        <v>24</v>
+      </c>
+      <c r="B153" t="s">
+        <v>49</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+      <c r="F153">
         <v>39.99</v>
       </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152">
-        <v>0</v>
-      </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-      <c r="J152">
-        <v>0</v>
-      </c>
-      <c r="K152">
-        <v>0</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152">
-        <v>0</v>
-      </c>
-      <c r="N152">
-        <v>0</v>
-      </c>
-      <c r="O152">
-        <v>0</v>
-      </c>
-      <c r="P152">
-        <v>0</v>
-      </c>
-      <c r="Q152" t="s">
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="s">
         <v>60</v>
       </c>
-      <c r="R152">
-        <v>0</v>
-      </c>
-      <c r="S152">
-        <v>0</v>
-      </c>
-      <c r="V152">
+      <c r="R153">
+        <v>0</v>
+      </c>
+      <c r="S153">
+        <v>0</v>
+      </c>
+      <c r="V153">
         <v>39.99</v>
       </c>
     </row>

--- a/refundable_samples_rollup.xlsx
+++ b/refundable_samples_rollup.xlsx
@@ -5686,16 +5686,16 @@
         <v>40</v>
       </c>
       <c r="C79">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D79">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E79">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F79">
-        <v>565.6799999999999</v>
+        <v>589.0700000000001</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -5731,10 +5731,10 @@
         <v>52</v>
       </c>
       <c r="R79">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="S79">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="T79">
         <v>35.6</v>
@@ -5743,7 +5743,7 @@
         <v>35.6</v>
       </c>
       <c r="V79">
-        <v>541.77</v>
+        <v>565.16</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -5754,16 +5754,16 @@
         <v>40</v>
       </c>
       <c r="C80">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D80">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E80">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F80">
-        <v>3096.64</v>
+        <v>3277.77</v>
       </c>
       <c r="G80">
         <v>4</v>
@@ -5778,13 +5778,13 @@
         <v>29.53</v>
       </c>
       <c r="K80">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L80">
         <v>0</v>
       </c>
       <c r="M80">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N80">
         <v>239.22</v>
@@ -5799,10 +5799,10 @@
         <v>53</v>
       </c>
       <c r="R80">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="S80">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="T80">
         <v>8.1</v>
@@ -5811,7 +5811,7 @@
         <v>8.1</v>
       </c>
       <c r="V80">
-        <v>2964.58</v>
+        <v>3145.71</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -5822,16 +5822,16 @@
         <v>40</v>
       </c>
       <c r="C81">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D81">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="E81">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="F81">
-        <v>6463.77</v>
+        <v>6851.97</v>
       </c>
       <c r="G81">
         <v>13</v>
@@ -5867,10 +5867,10 @@
         <v>54</v>
       </c>
       <c r="R81">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="S81">
-        <v>11.6</v>
+        <v>10.9</v>
       </c>
       <c r="T81">
         <v>11.4</v>
@@ -5879,7 +5879,7 @@
         <v>4.8</v>
       </c>
       <c r="V81">
-        <v>6051.23</v>
+        <v>6439.43</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -5890,37 +5890,37 @@
         <v>40</v>
       </c>
       <c r="C82">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="D82">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E82">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="F82">
-        <v>9824.559999999999</v>
+        <v>10319.91</v>
       </c>
       <c r="G82">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H82">
-        <v>1259.8</v>
+        <v>1379.77</v>
       </c>
       <c r="I82">
-        <v>555.6799999999999</v>
+        <v>634.67</v>
       </c>
       <c r="J82">
-        <v>156.44</v>
+        <v>178.53</v>
       </c>
       <c r="K82">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L82">
         <v>127</v>
       </c>
       <c r="M82">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N82">
         <v>432.43</v>
@@ -5935,19 +5935,19 @@
         <v>55</v>
       </c>
       <c r="R82">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="S82">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="T82">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="U82">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V82">
-        <v>9268.879999999999</v>
+        <v>9685.24</v>
       </c>
     </row>
     <row r="83" spans="1:22">
@@ -5958,28 +5958,28 @@
         <v>40</v>
       </c>
       <c r="C83">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D83">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="E83">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="F83">
-        <v>8709.120000000001</v>
+        <v>9219.99</v>
       </c>
       <c r="G83">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H83">
-        <v>1419.8</v>
+        <v>1459.79</v>
       </c>
       <c r="I83">
-        <v>623.85</v>
+        <v>646.0700000000001</v>
       </c>
       <c r="J83">
-        <v>173.21</v>
+        <v>178.9</v>
       </c>
       <c r="K83">
         <v>80</v>
@@ -6006,7 +6006,7 @@
         <v>7.2</v>
       </c>
       <c r="S83">
-        <v>10.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="T83">
         <v>0.7</v>
@@ -6015,7 +6015,7 @@
         <v>0.7</v>
       </c>
       <c r="V83">
-        <v>8085.27</v>
+        <v>8573.92</v>
       </c>
     </row>
     <row r="84" spans="1:22">
@@ -6026,28 +6026,28 @@
         <v>40</v>
       </c>
       <c r="C84">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D84">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E84">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F84">
-        <v>215.31</v>
+        <v>236.68</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>39.99</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>21.37</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="K84">
         <v>0</v>
@@ -6071,9 +6071,15 @@
         <v>57</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
         <v>0</v>
       </c>
       <c r="V84">
@@ -6088,28 +6094,28 @@
         <v>40</v>
       </c>
       <c r="C85">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D85">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E85">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F85">
-        <v>2360.48</v>
+        <v>2577.83</v>
       </c>
       <c r="G85">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H85">
-        <v>604.9</v>
+        <v>644.9</v>
       </c>
       <c r="I85">
-        <v>278.51</v>
+        <v>298.5</v>
       </c>
       <c r="J85">
-        <v>56.27</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="K85">
         <v>3</v>
@@ -6133,19 +6139,19 @@
         <v>58</v>
       </c>
       <c r="R85">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="S85">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="T85">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="U85">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="V85">
-        <v>2081.97</v>
+        <v>2279.33</v>
       </c>
     </row>
     <row r="86" spans="1:22">
@@ -6156,16 +6162,16 @@
         <v>40</v>
       </c>
       <c r="C86">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="D86">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="E86">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="F86">
-        <v>6557.21</v>
+        <v>7033.21</v>
       </c>
       <c r="G86">
         <v>8</v>
@@ -6180,13 +6186,13 @@
         <v>63.25</v>
       </c>
       <c r="K86">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L86">
         <v>5</v>
       </c>
       <c r="M86">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N86">
         <v>80.09</v>
@@ -6201,10 +6207,10 @@
         <v>59</v>
       </c>
       <c r="R86">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S86">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T86">
         <v>1.3</v>
@@ -6213,7 +6219,7 @@
         <v>1.3</v>
       </c>
       <c r="V86">
-        <v>6341.27</v>
+        <v>6817.27</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -6224,37 +6230,37 @@
         <v>40</v>
       </c>
       <c r="C87">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="D87">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="E87">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="F87">
-        <v>5486.67</v>
+        <v>5901.16</v>
       </c>
       <c r="G87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H87">
-        <v>229.98</v>
+        <v>274.98</v>
       </c>
       <c r="I87">
-        <v>113.34</v>
+        <v>128.18</v>
       </c>
       <c r="J87">
-        <v>37.04</v>
+        <v>42.73</v>
       </c>
       <c r="K87">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L87">
         <v>6</v>
       </c>
       <c r="M87">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N87">
         <v>151.8</v>
@@ -6269,19 +6275,19 @@
         <v>60</v>
       </c>
       <c r="R87">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="S87">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T87">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="U87">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="V87">
-        <v>5373.33</v>
+        <v>5772.98</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -6292,16 +6298,16 @@
         <v>40</v>
       </c>
       <c r="C88">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D88">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="E88">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="F88">
-        <v>4224.82</v>
+        <v>4703.32</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -6337,10 +6343,10 @@
         <v>61</v>
       </c>
       <c r="R88">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="S88">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="T88">
         <v>0</v>
@@ -6349,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="V88">
-        <v>4217.39</v>
+        <v>4695.89</v>
       </c>
     </row>
     <row r="89" spans="1:22">
@@ -6620,28 +6626,28 @@
         <v>41</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D93">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E93">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F93">
-        <v>195.97</v>
+        <v>225.96</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93">
-        <v>39.99</v>
+        <v>79.98</v>
       </c>
       <c r="I93">
-        <v>22.39</v>
+        <v>52.38</v>
       </c>
       <c r="J93">
-        <v>5.69</v>
+        <v>16.4</v>
       </c>
       <c r="K93">
         <v>12</v>
@@ -6665,13 +6671,13 @@
         <v>54</v>
       </c>
       <c r="R93">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="S93">
-        <v>42.9</v>
+        <v>37.5</v>
       </c>
       <c r="T93">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="U93">
         <v>0</v>
@@ -6824,16 +6830,16 @@
         <v>41</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96">
-        <v>26.3</v>
+        <v>34.87</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -6869,10 +6875,10 @@
         <v>58</v>
       </c>
       <c r="R96">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="S96">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T96">
         <v>5.1</v>
@@ -6881,7 +6887,7 @@
         <v>5.1</v>
       </c>
       <c r="V96">
-        <v>13.99</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="97" spans="1:22">
@@ -7690,16 +7696,16 @@
         <v>42</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E109">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F109">
-        <v>118.06</v>
+        <v>132.3</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -7741,7 +7747,7 @@
         <v>0</v>
       </c>
       <c r="V109">
-        <v>118.06</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="110" spans="1:22">
@@ -9726,16 +9732,16 @@
         <v>48</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D140">
+        <v>5</v>
+      </c>
+      <c r="E140">
         <v>6</v>
       </c>
-      <c r="E140">
-        <v>7</v>
-      </c>
       <c r="F140">
-        <v>160.81</v>
+        <v>137.42</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -9777,7 +9783,7 @@
         <v>0</v>
       </c>
       <c r="V140">
-        <v>160.81</v>
+        <v>137.42</v>
       </c>
     </row>
     <row r="141" spans="1:22">
@@ -9788,16 +9794,16 @@
         <v>48</v>
       </c>
       <c r="C141">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D141">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E141">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F141">
-        <v>574.41</v>
+        <v>393.28</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -9812,13 +9818,13 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
       <c r="M141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N141">
         <v>0</v>
@@ -9836,10 +9842,10 @@
         <v>0</v>
       </c>
       <c r="S141">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V141">
-        <v>574.41</v>
+        <v>393.28</v>
       </c>
     </row>
     <row r="142" spans="1:22">
@@ -9850,28 +9856,28 @@
         <v>48</v>
       </c>
       <c r="C142">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D142">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E142">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F142">
-        <v>1355.93</v>
+        <v>937.74</v>
       </c>
       <c r="G142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142">
-        <v>79.98</v>
+        <v>39.99</v>
       </c>
       <c r="I142">
-        <v>51.58</v>
+        <v>21.59</v>
       </c>
       <c r="J142">
-        <v>16.4</v>
+        <v>5.69</v>
       </c>
       <c r="K142">
         <v>0</v>
@@ -9895,7 +9901,7 @@
         <v>54</v>
       </c>
       <c r="R142">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="S142">
         <v>0</v>
@@ -9907,7 +9913,7 @@
         <v>0</v>
       </c>
       <c r="V142">
-        <v>1304.35</v>
+        <v>916.15</v>
       </c>
     </row>
     <row r="143" spans="1:22">
@@ -9918,37 +9924,37 @@
         <v>48</v>
       </c>
       <c r="C143">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D143">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E143">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F143">
-        <v>1806.25</v>
+        <v>1310.9</v>
       </c>
       <c r="G143">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H143">
-        <v>239.95</v>
+        <v>119.98</v>
       </c>
       <c r="I143">
-        <v>124.57</v>
+        <v>45.58</v>
       </c>
       <c r="J143">
-        <v>37.09</v>
+        <v>15</v>
       </c>
       <c r="K143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L143">
         <v>0</v>
       </c>
       <c r="M143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N143">
         <v>0</v>
@@ -9963,10 +9969,10 @@
         <v>55</v>
       </c>
       <c r="R143">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="S143">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="T143">
         <v>0</v>
@@ -9975,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="V143">
-        <v>1681.68</v>
+        <v>1265.32</v>
       </c>
     </row>
     <row r="144" spans="1:22">
@@ -9986,28 +9992,28 @@
         <v>48</v>
       </c>
       <c r="C144">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D144">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E144">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F144">
-        <v>1293.21</v>
+        <v>782.34</v>
       </c>
       <c r="G144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H144">
-        <v>119.98</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="I144">
-        <v>53.71</v>
+        <v>31.49</v>
       </c>
       <c r="J144">
-        <v>15</v>
+        <v>9.31</v>
       </c>
       <c r="K144">
         <v>2</v>
@@ -10031,10 +10037,10 @@
         <v>56</v>
       </c>
       <c r="R144">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="S144">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="T144">
         <v>0</v>
@@ -10043,7 +10049,7 @@
         <v>0</v>
       </c>
       <c r="V144">
-        <v>1239.5</v>
+        <v>750.85</v>
       </c>
     </row>
     <row r="145" spans="1:22">
@@ -10054,28 +10060,28 @@
         <v>48</v>
       </c>
       <c r="C145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145">
-        <v>43.86</v>
+        <v>22.49</v>
       </c>
       <c r="G145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>39.99</v>
+        <v>0</v>
       </c>
       <c r="I145">
-        <v>21.37</v>
+        <v>0</v>
       </c>
       <c r="J145">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -10099,15 +10105,9 @@
         <v>57</v>
       </c>
       <c r="R145">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S145">
-        <v>0</v>
-      </c>
-      <c r="T145">
-        <v>0</v>
-      </c>
-      <c r="U145">
         <v>0</v>
       </c>
       <c r="V145">
@@ -10122,28 +10122,28 @@
         <v>48</v>
       </c>
       <c r="C146">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D146">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E146">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F146">
-        <v>333.33</v>
+        <v>107.41</v>
       </c>
       <c r="G146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I146">
-        <v>19.99</v>
+        <v>0</v>
       </c>
       <c r="J146">
-        <v>8.970000000000001</v>
+        <v>0</v>
       </c>
       <c r="K146">
         <v>0</v>
@@ -10167,19 +10167,13 @@
         <v>58</v>
       </c>
       <c r="R146">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="S146">
         <v>0</v>
       </c>
-      <c r="T146">
-        <v>0</v>
-      </c>
-      <c r="U146">
-        <v>0</v>
-      </c>
       <c r="V146">
-        <v>313.34</v>
+        <v>107.41</v>
       </c>
     </row>
     <row r="147" spans="1:22">
@@ -10190,16 +10184,16 @@
         <v>48</v>
       </c>
       <c r="C147">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D147">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E147">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="F147">
-        <v>1052.67</v>
+        <v>576.67</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -10214,13 +10208,13 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L147">
         <v>0</v>
       </c>
       <c r="M147">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N147">
         <v>0</v>
@@ -10238,10 +10232,10 @@
         <v>0</v>
       </c>
       <c r="S147">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V147">
-        <v>1052.67</v>
+        <v>576.67</v>
       </c>
     </row>
     <row r="148" spans="1:22">
@@ -10252,37 +10246,37 @@
         <v>48</v>
       </c>
       <c r="C148">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D148">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E148">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F148">
-        <v>875.16</v>
+        <v>460.67</v>
       </c>
       <c r="G148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I148">
-        <v>14.84</v>
+        <v>0</v>
       </c>
       <c r="J148">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="K148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L148">
         <v>0</v>
       </c>
       <c r="M148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N148">
         <v>0</v>
@@ -10297,19 +10291,13 @@
         <v>60</v>
       </c>
       <c r="R148">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S148">
-        <v>2.4</v>
-      </c>
-      <c r="T148">
-        <v>0</v>
-      </c>
-      <c r="U148">
         <v>0</v>
       </c>
       <c r="V148">
-        <v>860.3200000000001</v>
+        <v>460.67</v>
       </c>
     </row>
     <row r="149" spans="1:22">
@@ -10320,16 +10308,16 @@
         <v>48</v>
       </c>
       <c r="C149">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D149">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E149">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F149">
-        <v>1070.4</v>
+        <v>577.66</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -10365,7 +10353,7 @@
         <v>61</v>
       </c>
       <c r="R149">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -10377,7 +10365,7 @@
         <v>0</v>
       </c>
       <c r="V149">
-        <v>1062.9</v>
+        <v>570.16</v>
       </c>
     </row>
     <row r="150" spans="1:22">

--- a/refundable_samples_rollup.xlsx
+++ b/refundable_samples_rollup.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="62">
   <si>
     <t>view</t>
   </si>
@@ -557,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V153"/>
+  <dimension ref="A1:V152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1384,16 +1384,16 @@
         <v>25</v>
       </c>
       <c r="C13">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="D13">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="E13">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="F13">
-        <v>5834.77</v>
+        <v>6189.84</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1429,10 +1429,10 @@
         <v>61</v>
       </c>
       <c r="R13">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S13">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T13">
         <v>6.3</v>
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="V13">
-        <v>5819.84</v>
+        <v>6174.91</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1514,16 +1514,16 @@
         <v>26</v>
       </c>
       <c r="C15">
+        <v>16</v>
+      </c>
+      <c r="D15">
         <v>15</v>
       </c>
-      <c r="D15">
-        <v>14</v>
-      </c>
       <c r="E15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>245.97</v>
+        <v>251.09</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1562,10 +1562,10 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="V15">
-        <v>245.97</v>
+        <v>251.09</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2658,16 +2658,16 @@
         <v>28</v>
       </c>
       <c r="C32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F32">
-        <v>3192.78</v>
+        <v>3383.42</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -2706,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="V32">
-        <v>3192.78</v>
+        <v>3383.42</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3172,16 +3172,16 @@
         <v>30</v>
       </c>
       <c r="C40">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D40">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E40">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F40">
-        <v>1154.73</v>
+        <v>1271.22</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V40">
-        <v>1154.73</v>
+        <v>1271.22</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3878,13 +3878,13 @@
         <v>34</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51">
         <v>23.43</v>
@@ -4188,16 +4188,16 @@
         <v>36</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56">
-        <v>68.69</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="V56">
-        <v>68.69</v>
+        <v>77.18000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4448,16 +4448,16 @@
         <v>37</v>
       </c>
       <c r="C60">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D60">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E60">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F60">
-        <v>444.4</v>
+        <v>470.91</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -4493,7 +4493,7 @@
         <v>61</v>
       </c>
       <c r="R60">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="V60">
-        <v>436.9</v>
+        <v>463.41</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -5500,16 +5500,16 @@
         <v>39</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76">
-        <v>36.98</v>
+        <v>44.8</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="V76">
-        <v>36.98</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -6162,16 +6162,16 @@
         <v>40</v>
       </c>
       <c r="C86">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D86">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E86">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F86">
-        <v>7441.63</v>
+        <v>7455.87</v>
       </c>
       <c r="G86">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.3</v>
       </c>
       <c r="V86">
-        <v>7225.69</v>
+        <v>7239.93</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -6230,16 +6230,16 @@
         <v>40</v>
       </c>
       <c r="C87">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D87">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E87">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F87">
-        <v>6241.05</v>
+        <v>6278.84</v>
       </c>
       <c r="G87">
         <v>7</v>
@@ -6287,7 +6287,7 @@
         <v>0.6</v>
       </c>
       <c r="V87">
-        <v>6112.87</v>
+        <v>6150.66</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -6298,16 +6298,16 @@
         <v>40</v>
       </c>
       <c r="C88">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D88">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E88">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F88">
-        <v>5258</v>
+        <v>5318.58</v>
       </c>
       <c r="G88">
         <v>2</v>
@@ -6355,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="V88">
-        <v>5243.07</v>
+        <v>5303.65</v>
       </c>
     </row>
     <row r="89" spans="1:22">
@@ -7696,16 +7696,16 @@
         <v>42</v>
       </c>
       <c r="C109">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D109">
+        <v>3</v>
+      </c>
+      <c r="E109">
         <v>4</v>
       </c>
-      <c r="E109">
-        <v>7</v>
-      </c>
       <c r="F109">
-        <v>132.3</v>
+        <v>103.36</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -7747,7 +7747,7 @@
         <v>0</v>
       </c>
       <c r="V109">
-        <v>132.3</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="110" spans="1:22">
@@ -10184,16 +10184,16 @@
         <v>48</v>
       </c>
       <c r="C147">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D147">
+        <v>10</v>
+      </c>
+      <c r="E147">
         <v>11</v>
       </c>
-      <c r="E147">
-        <v>12</v>
-      </c>
       <c r="F147">
-        <v>168.25</v>
+        <v>154.01</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="V147">
-        <v>168.25</v>
+        <v>154.01</v>
       </c>
     </row>
     <row r="148" spans="1:22">
@@ -10255,7 +10255,7 @@
         <v>6</v>
       </c>
       <c r="F148">
-        <v>120.78</v>
+        <v>122.98</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="V148">
-        <v>120.78</v>
+        <v>122.98</v>
       </c>
     </row>
     <row r="149" spans="1:22">
@@ -10308,16 +10308,16 @@
         <v>48</v>
       </c>
       <c r="C149">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D149">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E149">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F149">
-        <v>22.98</v>
+        <v>346.41</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -10359,7 +10359,7 @@
         <v>0</v>
       </c>
       <c r="V149">
-        <v>22.98</v>
+        <v>346.41</v>
       </c>
     </row>
     <row r="150" spans="1:22">
@@ -10552,68 +10552,6 @@
       </c>
       <c r="V152">
         <v>39.89</v>
-      </c>
-    </row>
-    <row r="153" spans="1:22">
-      <c r="A153" t="s">
-        <v>24</v>
-      </c>
-      <c r="B153" t="s">
-        <v>49</v>
-      </c>
-      <c r="C153">
-        <v>1</v>
-      </c>
-      <c r="D153">
-        <v>1</v>
-      </c>
-      <c r="E153">
-        <v>1</v>
-      </c>
-      <c r="F153">
-        <v>39.99</v>
-      </c>
-      <c r="G153">
-        <v>0</v>
-      </c>
-      <c r="H153">
-        <v>0</v>
-      </c>
-      <c r="I153">
-        <v>0</v>
-      </c>
-      <c r="J153">
-        <v>0</v>
-      </c>
-      <c r="K153">
-        <v>0</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153">
-        <v>0</v>
-      </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
-      <c r="O153">
-        <v>0</v>
-      </c>
-      <c r="P153">
-        <v>0</v>
-      </c>
-      <c r="Q153" t="s">
-        <v>60</v>
-      </c>
-      <c r="R153">
-        <v>0</v>
-      </c>
-      <c r="S153">
-        <v>0</v>
-      </c>
-      <c r="V153">
-        <v>39.99</v>
       </c>
     </row>
   </sheetData>

--- a/refundable_samples_rollup.xlsx
+++ b/refundable_samples_rollup.xlsx
@@ -6230,16 +6230,16 @@
         <v>40</v>
       </c>
       <c r="C87">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D87">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E87">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F87">
-        <v>6278.84</v>
+        <v>6318.83</v>
       </c>
       <c r="G87">
         <v>7</v>
@@ -6287,7 +6287,7 @@
         <v>0.6</v>
       </c>
       <c r="V87">
-        <v>6150.66</v>
+        <v>6190.65</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -6298,16 +6298,16 @@
         <v>40</v>
       </c>
       <c r="C88">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D88">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E88">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="F88">
-        <v>5318.58</v>
+        <v>5518.33</v>
       </c>
       <c r="G88">
         <v>2</v>
@@ -6343,10 +6343,10 @@
         <v>61</v>
       </c>
       <c r="R88">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S88">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T88">
         <v>0</v>
@@ -6355,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="V88">
-        <v>5303.65</v>
+        <v>5503.4</v>
       </c>
     </row>
     <row r="89" spans="1:22">
@@ -10246,16 +10246,16 @@
         <v>48</v>
       </c>
       <c r="C148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F148">
-        <v>122.98</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="V148">
-        <v>122.98</v>
+        <v>82.98999999999999</v>
       </c>
     </row>
     <row r="149" spans="1:22">
@@ -10308,16 +10308,16 @@
         <v>48</v>
       </c>
       <c r="C149">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D149">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E149">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F149">
-        <v>346.41</v>
+        <v>146.66</v>
       </c>
       <c r="G149">
         <v>0</v>
@@ -10359,7 +10359,7 @@
         <v>0</v>
       </c>
       <c r="V149">
-        <v>346.41</v>
+        <v>146.66</v>
       </c>
     </row>
     <row r="150" spans="1:22">

--- a/refundable_samples_rollup.xlsx
+++ b/refundable_samples_rollup.xlsx
@@ -1263,16 +1263,16 @@
         <v>8230.629999999999</v>
       </c>
       <c r="G11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H11">
-        <v>659.98</v>
+        <v>779.97</v>
       </c>
       <c r="I11">
-        <v>277.12</v>
+        <v>331.11</v>
       </c>
       <c r="J11">
-        <v>97.95999999999999</v>
+        <v>103.65</v>
       </c>
       <c r="K11">
         <v>49</v>
@@ -1296,19 +1296,19 @@
         <v>60</v>
       </c>
       <c r="R11">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="S11">
         <v>6.5</v>
       </c>
       <c r="T11">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U11">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="V11">
-        <v>7953.51</v>
+        <v>7899.52</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1399,16 +1399,16 @@
         <v>7927.81</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>39.99</v>
+        <v>59.98</v>
       </c>
       <c r="I13">
-        <v>14.93</v>
+        <v>24.92</v>
       </c>
       <c r="J13">
-        <v>9.59</v>
+        <v>14.45</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1432,19 +1432,19 @@
         <v>62</v>
       </c>
       <c r="R13">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="S13">
         <v>2.4</v>
       </c>
       <c r="T13">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
       <c r="U13">
         <v>0</v>
       </c>
       <c r="V13">
-        <v>7912.88</v>
+        <v>7902.89</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2537,16 +2537,16 @@
         <v>6537</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H30">
-        <v>579.98</v>
+        <v>699.97</v>
       </c>
       <c r="I30">
-        <v>254.96</v>
+        <v>308.95</v>
       </c>
       <c r="J30">
-        <v>80.02</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="K30">
         <v>43</v>
@@ -2570,19 +2570,19 @@
         <v>60</v>
       </c>
       <c r="R30">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="S30">
         <v>7.2</v>
       </c>
       <c r="T30">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U30">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="V30">
-        <v>6282.04</v>
+        <v>6228.05</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -4525,16 +4525,16 @@
         <v>583.5599999999999</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>19.99</v>
+        <v>39.98</v>
       </c>
       <c r="I61">
-        <v>7.5</v>
+        <v>17.49</v>
       </c>
       <c r="J61">
-        <v>4.86</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -4558,7 +4558,7 @@
         <v>62</v>
       </c>
       <c r="R61">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="V61">
-        <v>576.0599999999999</v>
+        <v>566.0700000000001</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -6239,16 +6239,16 @@
         <v>7455.87</v>
       </c>
       <c r="G87">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H87">
-        <v>539.98</v>
+        <v>659.97</v>
       </c>
       <c r="I87">
-        <v>215.94</v>
+        <v>269.93</v>
       </c>
       <c r="J87">
-        <v>63.25</v>
+        <v>68.94</v>
       </c>
       <c r="K87">
         <v>21</v>
@@ -6272,19 +6272,19 @@
         <v>60</v>
       </c>
       <c r="R87">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S87">
         <v>3.7</v>
       </c>
       <c r="T87">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="U87">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="V87">
-        <v>7239.93</v>
+        <v>7185.94</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -6375,16 +6375,16 @@
         <v>6743.02</v>
       </c>
       <c r="G89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H89">
-        <v>39.99</v>
+        <v>59.98</v>
       </c>
       <c r="I89">
-        <v>14.93</v>
+        <v>24.92</v>
       </c>
       <c r="J89">
-        <v>9.59</v>
+        <v>14.45</v>
       </c>
       <c r="K89">
         <v>4</v>
@@ -6408,7 +6408,7 @@
         <v>62</v>
       </c>
       <c r="R89">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="S89">
         <v>1.2</v>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="V89">
-        <v>6728.09</v>
+        <v>6718.1</v>
       </c>
     </row>
     <row r="90" spans="1:22">

--- a/refundable_samples_rollup.xlsx
+++ b/refundable_samples_rollup.xlsx
@@ -731,10 +731,10 @@
         <v>23.79</v>
       </c>
       <c r="K3">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M3">
         <v>8</v>
@@ -1003,10 +1003,10 @@
         <v>314.7</v>
       </c>
       <c r="K7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M7">
         <v>53</v>
@@ -1071,7 +1071,7 @@
         <v>324.47</v>
       </c>
       <c r="K8">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L8">
         <v>130</v>
@@ -1080,13 +1080,13 @@
         <v>49</v>
       </c>
       <c r="N8">
-        <v>5821.13</v>
+        <v>6206.48</v>
       </c>
       <c r="O8">
         <v>1209.99</v>
       </c>
       <c r="P8">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q8" t="s">
         <v>57</v>
@@ -1098,7 +1098,7 @@
         <v>14.3</v>
       </c>
       <c r="T8">
-        <v>17.9</v>
+        <v>19.1</v>
       </c>
       <c r="U8">
         <v>3.7</v>
@@ -1148,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>344.16</v>
+        <v>330.09</v>
       </c>
       <c r="O9">
-        <v>344.16</v>
+        <v>330.09</v>
       </c>
       <c r="P9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="s">
         <v>58</v>
@@ -1166,10 +1166,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="T9">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="U9">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="V9">
         <v>237.8</v>
@@ -1275,22 +1275,22 @@
         <v>103.65</v>
       </c>
       <c r="K11">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L11">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N11">
-        <v>145.15</v>
+        <v>125.16</v>
       </c>
       <c r="O11">
-        <v>104.79</v>
+        <v>84.8</v>
       </c>
       <c r="P11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="s">
         <v>60</v>
@@ -1299,13 +1299,13 @@
         <v>3.2</v>
       </c>
       <c r="S11">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="T11">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="V11">
         <v>7899.52</v>
@@ -1343,13 +1343,13 @@
         <v>54.11</v>
       </c>
       <c r="K12">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L12">
         <v>11</v>
       </c>
       <c r="M12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N12">
         <v>470.92</v>
@@ -1367,7 +1367,7 @@
         <v>3.1</v>
       </c>
       <c r="S12">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="T12">
         <v>8.699999999999999</v>
@@ -1411,13 +1411,13 @@
         <v>14.45</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>59.99</v>
@@ -1435,7 +1435,7 @@
         <v>1</v>
       </c>
       <c r="S13">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="T13">
         <v>4.2</v>
@@ -2073,10 +2073,10 @@
         <v>18.15</v>
       </c>
       <c r="K23">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L23">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M23">
         <v>7</v>
@@ -2345,10 +2345,10 @@
         <v>274.75</v>
       </c>
       <c r="K27">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L27">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M27">
         <v>49</v>
@@ -2413,7 +2413,7 @@
         <v>265.63</v>
       </c>
       <c r="K28">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L28">
         <v>130</v>
@@ -2422,13 +2422,13 @@
         <v>47</v>
       </c>
       <c r="N28">
-        <v>5802.14</v>
+        <v>6187.49</v>
       </c>
       <c r="O28">
         <v>1191</v>
       </c>
       <c r="P28">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q28" t="s">
         <v>57</v>
@@ -2440,7 +2440,7 @@
         <v>14.2</v>
       </c>
       <c r="T28">
-        <v>21.8</v>
+        <v>23.3</v>
       </c>
       <c r="U28">
         <v>4.5</v>
@@ -2549,10 +2549,10 @@
         <v>85.70999999999999</v>
       </c>
       <c r="K30">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L30">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M30">
         <v>19</v>
@@ -2617,13 +2617,13 @@
         <v>42.72</v>
       </c>
       <c r="K31">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L31">
         <v>9</v>
       </c>
       <c r="M31">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N31">
         <v>460.89</v>
@@ -2641,7 +2641,7 @@
         <v>4.9</v>
       </c>
       <c r="S31">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="T31">
         <v>10.8</v>
@@ -2685,10 +2685,10 @@
         <v>0</v>
       </c>
       <c r="K32">
+        <v>11</v>
+      </c>
+      <c r="L32">
         <v>7</v>
-      </c>
-      <c r="L32">
-        <v>4</v>
       </c>
       <c r="M32">
         <v>5</v>
@@ -3063,7 +3063,7 @@
         <v>22.56</v>
       </c>
       <c r="K38">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3199,13 +3199,13 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V40">
         <v>1594.58</v>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -4407,22 +4407,22 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N59">
-        <v>19.99</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>19.99</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="s">
         <v>60</v>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="S59">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="V59">
         <v>435.57</v>
@@ -4874,13 +4874,13 @@
         <v>1</v>
       </c>
       <c r="N66">
-        <v>344.16</v>
+        <v>330.09</v>
       </c>
       <c r="O66">
-        <v>344.16</v>
+        <v>330.09</v>
       </c>
       <c r="P66">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q66" t="s">
         <v>58</v>
@@ -4892,10 +4892,10 @@
         <v>10</v>
       </c>
       <c r="T66">
-        <v>52.7</v>
+        <v>50.5</v>
       </c>
       <c r="U66">
-        <v>52.7</v>
+        <v>50.5</v>
       </c>
       <c r="V66">
         <v>220.21</v>
@@ -5979,10 +5979,10 @@
         <v>178.53</v>
       </c>
       <c r="K83">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L83">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M83">
         <v>36</v>
@@ -6254,19 +6254,19 @@
         <v>21</v>
       </c>
       <c r="L87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M87">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N87">
-        <v>80.09</v>
+        <v>60.1</v>
       </c>
       <c r="O87">
-        <v>80.09</v>
+        <v>60.1</v>
       </c>
       <c r="P87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="s">
         <v>60</v>
@@ -6275,13 +6275,13 @@
         <v>2.4</v>
       </c>
       <c r="S87">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T87">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="U87">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="V87">
         <v>7185.94</v>
@@ -6319,13 +6319,13 @@
         <v>42.73</v>
       </c>
       <c r="K88">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L88">
         <v>6</v>
       </c>
       <c r="M88">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N88">
         <v>151.8</v>
@@ -6343,7 +6343,7 @@
         <v>2.7</v>
       </c>
       <c r="S88">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="T88">
         <v>3.6</v>
@@ -6363,16 +6363,16 @@
         <v>41</v>
       </c>
       <c r="C89">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D89">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E89">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F89">
-        <v>6984.26</v>
+        <v>7075.34</v>
       </c>
       <c r="G89">
         <v>3</v>
@@ -6387,13 +6387,13 @@
         <v>14.45</v>
       </c>
       <c r="K89">
+        <v>6</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
         <v>4</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>3</v>
       </c>
       <c r="N89">
         <v>0</v>
@@ -6411,7 +6411,7 @@
         <v>1.1</v>
       </c>
       <c r="S89">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="T89">
         <v>0</v>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="V89">
-        <v>6959.34</v>
+        <v>7050.42</v>
       </c>
     </row>
     <row r="90" spans="1:22">
@@ -7055,7 +7055,7 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L99">
         <v>1</v>
@@ -7117,10 +7117,10 @@
         <v>0</v>
       </c>
       <c r="K100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M100">
         <v>1</v>
@@ -7445,10 +7445,10 @@
         <v>23.84</v>
       </c>
       <c r="K105">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L105">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M105">
         <v>5</v>
@@ -7649,10 +7649,10 @@
         <v>26.13</v>
       </c>
       <c r="K108">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L108">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M108">
         <v>6</v>
@@ -7717,7 +7717,7 @@
         <v>5.69</v>
       </c>
       <c r="K109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L109">
         <v>0</v>
@@ -7909,10 +7909,10 @@
         <v>18.15</v>
       </c>
       <c r="K112">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L112">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M112">
         <v>2</v>
@@ -8184,7 +8184,7 @@
         <v>56</v>
       </c>
       <c r="L116">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M116">
         <v>7</v>
@@ -8249,10 +8249,10 @@
         <v>50.55</v>
       </c>
       <c r="K117">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L117">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M117">
         <v>6</v>
@@ -8515,10 +8515,10 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L121">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M121">
         <v>2</v>
@@ -8707,22 +8707,22 @@
         <v>11.38</v>
       </c>
       <c r="K124">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L124">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M124">
         <v>2</v>
       </c>
       <c r="N124">
-        <v>4665.1</v>
+        <v>5050.45</v>
       </c>
       <c r="O124">
         <v>277.62</v>
       </c>
       <c r="P124">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Q124" t="s">
         <v>57</v>
@@ -8734,7 +8734,7 @@
         <v>100</v>
       </c>
       <c r="T124">
-        <v>409.9</v>
+        <v>443.8</v>
       </c>
       <c r="U124">
         <v>24.4</v>
@@ -9425,7 +9425,7 @@
         <v>5.69</v>
       </c>
       <c r="K135">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L135">
         <v>0</v>
@@ -9502,13 +9502,13 @@
         <v>1</v>
       </c>
       <c r="N136">
-        <v>344.16</v>
+        <v>330.09</v>
       </c>
       <c r="O136">
-        <v>344.16</v>
+        <v>330.09</v>
       </c>
       <c r="P136">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q136" t="s">
         <v>58</v>
@@ -9520,10 +9520,10 @@
         <v>100</v>
       </c>
       <c r="T136">
-        <v>52.7</v>
+        <v>50.5</v>
       </c>
       <c r="U136">
-        <v>52.7</v>
+        <v>50.5</v>
       </c>
       <c r="V136">
         <v>0</v>
@@ -10373,16 +10373,16 @@
         <v>49</v>
       </c>
       <c r="C150">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D150">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E150">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F150">
-        <v>322.66</v>
+        <v>231.58</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -10424,7 +10424,7 @@
         <v>0</v>
       </c>
       <c r="V150">
-        <v>322.66</v>
+        <v>231.58</v>
       </c>
     </row>
     <row r="151" spans="1:22">

--- a/refundable_samples_rollup.xlsx
+++ b/refundable_samples_rollup.xlsx
@@ -6363,16 +6363,16 @@
         <v>41</v>
       </c>
       <c r="C89">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="D89">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="E89">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="F89">
-        <v>7121.02</v>
+        <v>7532.91</v>
       </c>
       <c r="G89">
         <v>3</v>
@@ -6408,10 +6408,10 @@
         <v>62</v>
       </c>
       <c r="R89">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="S89">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
         <v>0</v>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="V89">
-        <v>7096.1</v>
+        <v>7507.99</v>
       </c>
     </row>
     <row r="90" spans="1:22">
@@ -7761,16 +7761,16 @@
         <v>43</v>
       </c>
       <c r="C110">
+        <v>6</v>
+      </c>
+      <c r="D110">
         <v>5</v>
       </c>
-      <c r="D110">
-        <v>4</v>
-      </c>
       <c r="E110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F110">
-        <v>149.35</v>
+        <v>158.74</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -7812,7 +7812,7 @@
         <v>0</v>
       </c>
       <c r="V110">
-        <v>149.35</v>
+        <v>158.74</v>
       </c>
     </row>
     <row r="111" spans="1:22">
@@ -10373,16 +10373,16 @@
         <v>49</v>
       </c>
       <c r="C150">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D150">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E150">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F150">
-        <v>652.86</v>
+        <v>231.58</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -10424,7 +10424,7 @@
         <v>0</v>
       </c>
       <c r="V150">
-        <v>652.86</v>
+        <v>231.58</v>
       </c>
     </row>
     <row r="151" spans="1:22">

--- a/refundable_samples_rollup.xlsx
+++ b/refundable_samples_rollup.xlsx
@@ -731,22 +731,22 @@
         <v>23.79</v>
       </c>
       <c r="K3">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M3">
         <v>8</v>
       </c>
       <c r="N3">
-        <v>1426.69</v>
+        <v>1460.98</v>
       </c>
       <c r="O3">
         <v>1041.12</v>
       </c>
       <c r="P3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="s">
         <v>52</v>
@@ -758,7 +758,7 @@
         <v>66.7</v>
       </c>
       <c r="T3">
-        <v>60</v>
+        <v>61.4</v>
       </c>
       <c r="U3">
         <v>43.8</v>
@@ -808,10 +808,10 @@
         <v>16</v>
       </c>
       <c r="N4">
-        <v>5469.14</v>
+        <v>5469.15</v>
       </c>
       <c r="O4">
-        <v>1281.25</v>
+        <v>1281.26</v>
       </c>
       <c r="P4">
         <v>163</v>
@@ -867,10 +867,10 @@
         <v>94.45</v>
       </c>
       <c r="K5">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M5">
         <v>20</v>
@@ -1071,7 +1071,7 @@
         <v>324.47</v>
       </c>
       <c r="K8">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L8">
         <v>132</v>
@@ -1080,13 +1080,13 @@
         <v>49</v>
       </c>
       <c r="N8">
-        <v>6431.18</v>
+        <v>6394.27</v>
       </c>
       <c r="O8">
         <v>1209.99</v>
       </c>
       <c r="P8">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="Q8" t="s">
         <v>57</v>
@@ -1098,7 +1098,7 @@
         <v>14.3</v>
       </c>
       <c r="T8">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="U8">
         <v>3.7</v>
@@ -1387,16 +1387,16 @@
         <v>25</v>
       </c>
       <c r="C13">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="D13">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="E13">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="F13">
-        <v>9221.190000000001</v>
+        <v>10020.29</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -1411,16 +1411,16 @@
         <v>14.45</v>
       </c>
       <c r="K13">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N13">
-        <v>129.27</v>
+        <v>129.29</v>
       </c>
       <c r="O13">
         <v>14.29</v>
@@ -1444,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="V13">
-        <v>9196.27</v>
+        <v>9995.370000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1517,16 +1517,16 @@
         <v>26</v>
       </c>
       <c r="C15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>372.24</v>
+        <v>411.38</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1541,13 +1541,13 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>12.5</v>
+        <v>14.8</v>
       </c>
       <c r="V15">
-        <v>372.24</v>
+        <v>411.38</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2073,22 +2073,22 @@
         <v>18.15</v>
       </c>
       <c r="K23">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L23">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M23">
         <v>7</v>
       </c>
       <c r="N23">
-        <v>586.4</v>
+        <v>620.6900000000001</v>
       </c>
       <c r="O23">
         <v>200.83</v>
       </c>
       <c r="P23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="s">
         <v>52</v>
@@ -2100,7 +2100,7 @@
         <v>63.6</v>
       </c>
       <c r="T23">
-        <v>32.3</v>
+        <v>34.2</v>
       </c>
       <c r="U23">
         <v>11.1</v>
@@ -2150,10 +2150,10 @@
         <v>14</v>
       </c>
       <c r="N24">
-        <v>5469.14</v>
+        <v>5469.15</v>
       </c>
       <c r="O24">
-        <v>1281.25</v>
+        <v>1281.26</v>
       </c>
       <c r="P24">
         <v>163</v>
@@ -2209,10 +2209,10 @@
         <v>75.14</v>
       </c>
       <c r="K25">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L25">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M25">
         <v>19</v>
@@ -2413,7 +2413,7 @@
         <v>265.63</v>
       </c>
       <c r="K28">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L28">
         <v>132</v>
@@ -2422,13 +2422,13 @@
         <v>47</v>
       </c>
       <c r="N28">
-        <v>6412.19</v>
+        <v>6375.28</v>
       </c>
       <c r="O28">
         <v>1191</v>
       </c>
       <c r="P28">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="Q28" t="s">
         <v>57</v>
@@ -2440,7 +2440,7 @@
         <v>14.2</v>
       </c>
       <c r="T28">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="U28">
         <v>4.5</v>
@@ -2661,16 +2661,16 @@
         <v>28</v>
       </c>
       <c r="C32">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D32">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E32">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F32">
-        <v>5157.73</v>
+        <v>5661</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -2694,7 +2694,7 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>114.98</v>
+        <v>115</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -2709,10 +2709,10 @@
         <v>0</v>
       </c>
       <c r="S32">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="V32">
-        <v>5157.73</v>
+        <v>5661</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3175,16 +3175,16 @@
         <v>30</v>
       </c>
       <c r="C40">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D40">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E40">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F40">
-        <v>1876.97</v>
+        <v>2047.83</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         <v>0</v>
       </c>
       <c r="S40">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="V40">
-        <v>1876.97</v>
+        <v>2047.83</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3435,16 +3435,16 @@
         <v>31</v>
       </c>
       <c r="C44">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D44">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E44">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F44">
-        <v>259.38</v>
+        <v>279.61</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="V44">
-        <v>259.38</v>
+        <v>279.61</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -3751,16 +3751,16 @@
         <v>33</v>
       </c>
       <c r="C49">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D49">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E49">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F49">
-        <v>257.41</v>
+        <v>282.08</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -3796,7 +3796,7 @@
         <v>62</v>
       </c>
       <c r="R49">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -3808,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="V49">
-        <v>249.98</v>
+        <v>274.65</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -3881,13 +3881,13 @@
         <v>34</v>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F51">
         <v>23.43</v>
@@ -4513,16 +4513,16 @@
         <v>38</v>
       </c>
       <c r="C61">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D61">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E61">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F61">
-        <v>638.78</v>
+        <v>665.47</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -4558,7 +4558,7 @@
         <v>62</v>
       </c>
       <c r="R61">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="V61">
-        <v>621.29</v>
+        <v>647.98</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -5107,16 +5107,16 @@
         <v>39</v>
       </c>
       <c r="C70">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D70">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E70">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F70">
-        <v>90.48</v>
+        <v>104.72</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="V70">
-        <v>90.48</v>
+        <v>104.72</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5713,22 +5713,22 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M79">
         <v>5</v>
       </c>
       <c r="N79">
-        <v>200.83</v>
+        <v>235.12</v>
       </c>
       <c r="O79">
         <v>200.83</v>
       </c>
       <c r="P79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q79" t="s">
         <v>52</v>
@@ -5979,10 +5979,10 @@
         <v>178.53</v>
       </c>
       <c r="K83">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L83">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M83">
         <v>36</v>
@@ -6047,7 +6047,7 @@
         <v>178.9</v>
       </c>
       <c r="K84">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L84">
         <v>28</v>
@@ -6159,16 +6159,16 @@
         <v>41</v>
       </c>
       <c r="C86">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D86">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E86">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F86">
-        <v>2641.32</v>
+        <v>2603.88</v>
       </c>
       <c r="G86">
         <v>11</v>
@@ -6204,7 +6204,7 @@
         <v>59</v>
       </c>
       <c r="R86">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S86">
         <v>1.6</v>
@@ -6216,7 +6216,7 @@
         <v>0.2</v>
       </c>
       <c r="V86">
-        <v>2342.82</v>
+        <v>2305.38</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -6363,16 +6363,16 @@
         <v>41</v>
       </c>
       <c r="C89">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D89">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E89">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="F89">
-        <v>8149.32</v>
+        <v>8314.4</v>
       </c>
       <c r="G89">
         <v>3</v>
@@ -6387,13 +6387,13 @@
         <v>14.45</v>
       </c>
       <c r="K89">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
       <c r="M89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N89">
         <v>0</v>
@@ -6411,7 +6411,7 @@
         <v>0.9</v>
       </c>
       <c r="S89">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="T89">
         <v>0</v>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="V89">
-        <v>8124.4</v>
+        <v>8289.48</v>
       </c>
     </row>
     <row r="90" spans="1:22">
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M93">
         <v>1</v>
@@ -7093,16 +7093,16 @@
         <v>42</v>
       </c>
       <c r="C100">
+        <v>14</v>
+      </c>
+      <c r="D100">
         <v>13</v>
       </c>
-      <c r="D100">
-        <v>12</v>
-      </c>
       <c r="E100">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F100">
-        <v>342.93</v>
+        <v>355.73</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>2</v>
       </c>
       <c r="N100">
-        <v>69.28</v>
+        <v>69.3</v>
       </c>
       <c r="O100">
         <v>14.29</v>
@@ -7141,10 +7141,10 @@
         <v>0</v>
       </c>
       <c r="S100">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="V100">
-        <v>342.93</v>
+        <v>355.73</v>
       </c>
     </row>
     <row r="101" spans="1:22">
@@ -7445,10 +7445,10 @@
         <v>23.84</v>
       </c>
       <c r="K105">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L105">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M105">
         <v>5</v>
@@ -8491,16 +8491,16 @@
         <v>44</v>
       </c>
       <c r="C121">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E121">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F121">
-        <v>156.2</v>
+        <v>239.82</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -8539,10 +8539,10 @@
         <v>0</v>
       </c>
       <c r="S121">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="V121">
-        <v>156.2</v>
+        <v>239.82</v>
       </c>
     </row>
     <row r="122" spans="1:22">
@@ -8716,13 +8716,13 @@
         <v>2</v>
       </c>
       <c r="N124">
-        <v>5275.15</v>
+        <v>5238.24</v>
       </c>
       <c r="O124">
         <v>277.62</v>
       </c>
       <c r="P124">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q124" t="s">
         <v>57</v>
@@ -8734,7 +8734,7 @@
         <v>100</v>
       </c>
       <c r="T124">
-        <v>463.5</v>
+        <v>460.3</v>
       </c>
       <c r="U124">
         <v>24.4</v>
@@ -8970,10 +8970,10 @@
         <v>1</v>
       </c>
       <c r="N128">
-        <v>1078.92</v>
+        <v>1078.93</v>
       </c>
       <c r="O128">
-        <v>1078.92</v>
+        <v>1078.93</v>
       </c>
       <c r="P128">
         <v>26</v>
@@ -9697,10 +9697,10 @@
         <v>0</v>
       </c>
       <c r="K139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M139">
         <v>1</v>
@@ -10187,16 +10187,16 @@
         <v>49</v>
       </c>
       <c r="C147">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D147">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E147">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F147">
-        <v>43.92</v>
+        <v>81.36</v>
       </c>
       <c r="G147">
         <v>0</v>
@@ -10238,7 +10238,7 @@
         <v>0</v>
       </c>
       <c r="V147">
-        <v>43.92</v>
+        <v>81.36</v>
       </c>
     </row>
     <row r="148" spans="1:22">
@@ -10373,16 +10373,16 @@
         <v>49</v>
       </c>
       <c r="C150">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D150">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E150">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F150">
-        <v>276.57</v>
+        <v>814.17</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -10424,7 +10424,7 @@
         <v>0</v>
       </c>
       <c r="V150">
-        <v>276.57</v>
+        <v>814.17</v>
       </c>
     </row>
     <row r="151" spans="1:22">
